--- a/nablarch_sample/アプリケーション方式設計書_0表紙.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_0表紙.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26130"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2756DE6B-18B7-4112-ADE0-36B6D20A0998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801E80A1-FADB-451F-9C8D-77B74FD78568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="-120" windowWidth="27765" windowHeight="16440" tabRatio="683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" tabRatio="683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="19" r:id="rId1"/>
@@ -18,11 +18,14 @@
     <definedName name="_Toc77519345" localSheetId="2">目次!#REF!</definedName>
     <definedName name="_Toc77519346" localSheetId="2">目次!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$AI$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">目次!$A$1:$AI$133</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">目次!$A$1:$AI$152</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">目次!$1:$4</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="manual"/>
+  <calcPr calcId="191028" calcMode="manual"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -30,6 +33,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,253 +42,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="147">
-  <si>
-    <t>PJ名</t>
-  </si>
-  <si>
-    <t>XXXプロジェクト</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>工程</t>
-  </si>
-  <si>
-    <t>要件定義</t>
-    <rPh sb="0" eb="2">
-      <t>ヨウケン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>テイギ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>作成</t>
-    <rPh sb="0" eb="2">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>システム名</t>
-  </si>
-  <si>
-    <t>成果物名</t>
-  </si>
-  <si>
-    <t>アプリケーション方式設計書</t>
-    <rPh sb="8" eb="10">
-      <t>ホウシキ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>セッケイショ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>変更</t>
-    <rPh sb="0" eb="2">
-      <t>ヘンコウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>業務グループ名</t>
-    <rPh sb="0" eb="2">
-      <t>ギョウム</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>変更履歴（ 1　/ 1 ）</t>
-  </si>
-  <si>
-    <t>No.</t>
-    <phoneticPr fontId="50"/>
-  </si>
-  <si>
-    <t>版数</t>
-    <rPh sb="0" eb="2">
-      <t>ハンスウ</t>
-    </rPh>
-    <phoneticPr fontId="50"/>
-  </si>
-  <si>
-    <t>変更日</t>
-    <rPh sb="0" eb="3">
-      <t>ヘンコウビ</t>
-    </rPh>
-    <phoneticPr fontId="50"/>
-  </si>
-  <si>
-    <t>区分</t>
-    <rPh sb="0" eb="2">
-      <t>クブン</t>
-    </rPh>
-    <phoneticPr fontId="50"/>
-  </si>
-  <si>
-    <t>変更箇所</t>
-    <rPh sb="0" eb="2">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カショ</t>
-    </rPh>
-    <phoneticPr fontId="50"/>
-  </si>
-  <si>
-    <t>変更内容</t>
-    <rPh sb="0" eb="2">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="50"/>
-  </si>
-  <si>
-    <t>担当者</t>
-    <rPh sb="0" eb="3">
-      <t>タントウシャ</t>
-    </rPh>
-    <phoneticPr fontId="50"/>
-  </si>
-  <si>
-    <t>頁</t>
-    <rPh sb="0" eb="1">
-      <t>ページ</t>
-    </rPh>
-    <phoneticPr fontId="50"/>
-  </si>
-  <si>
-    <t>項番</t>
-    <rPh sb="0" eb="1">
-      <t>コウ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>バン</t>
-    </rPh>
-    <phoneticPr fontId="50"/>
-  </si>
-  <si>
-    <t>1.0</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>新規</t>
-    <rPh sb="0" eb="2">
-      <t>シンキ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>新規作成</t>
-    <rPh sb="0" eb="2">
-      <t>シンキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>TISXXX</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>目次（１／１）</t>
-  </si>
-  <si>
-    <t>1.はじめに</t>
-  </si>
-  <si>
-    <t>2.全体概要</t>
-  </si>
-  <si>
-    <t>3.画面処理方式</t>
-  </si>
-  <si>
-    <t>3.1.同期処理方式</t>
-  </si>
-  <si>
-    <t>3.2.非同期処理方式</t>
-  </si>
-  <si>
-    <t>4.バッチ処理方式</t>
-  </si>
-  <si>
-    <t>4.1.都度起動バッチ</t>
-  </si>
-  <si>
-    <t>4.2.常駐バッチ</t>
-  </si>
-  <si>
-    <t>5.入力処理方式</t>
-  </si>
-  <si>
-    <t>5.1.ファイル転送(集信)</t>
-  </si>
-  <si>
-    <t>6.出力処理方式</t>
-  </si>
-  <si>
-    <t>6.1.メッセージ仕向け(REST)</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>6.2.ファイル転送(配信)</t>
-  </si>
-  <si>
-    <t>6.3.メール送信</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>7.処理方式共通</t>
-  </si>
-  <si>
-    <t>7.1.入力値精査</t>
-  </si>
-  <si>
-    <t>7.2.文字コード</t>
-  </si>
-  <si>
-    <t>7.3.DBアクセス処理</t>
-  </si>
-  <si>
-    <t>7.4.ファイルアクセス処理</t>
-  </si>
-  <si>
-    <t>7.5.認証・認可</t>
-  </si>
-  <si>
-    <t>7.6.メッセージ管理方式</t>
-  </si>
-  <si>
-    <t>7.7.コード管理方式</t>
-  </si>
-  <si>
-    <t>7.8.採番方式</t>
-  </si>
-  <si>
-    <t>7.9.日付・時刻処理方式</t>
-  </si>
-  <si>
-    <t>7.10.ファイル管理</t>
-  </si>
-  <si>
-    <t>7.11.暗号化・ハッシュ化</t>
-  </si>
-  <si>
-    <t>7.13.ログ</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>20XX/XX/XX</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="166">
+  <si>
+    <t>第1.0版</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -300,8 +61,556 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>第1.0版</t>
+    <t>PJ名</t>
+  </si>
+  <si>
+    <t>XXXプロジェクト</t>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>工程</t>
+  </si>
+  <si>
+    <t>要件定義</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>作成</t>
+    <rPh sb="0" eb="2">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>システム名</t>
+  </si>
+  <si>
+    <t>成果物名</t>
+  </si>
+  <si>
+    <t>アプリケーション方式設計書</t>
+    <rPh sb="8" eb="10">
+      <t>ホウシキ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>セッケイショ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>変更</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>業務グループ名</t>
+    <rPh sb="0" eb="2">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>変更履歴（ 1　/ 1 ）</t>
+  </si>
+  <si>
+    <t>No.</t>
+    <phoneticPr fontId="50"/>
+  </si>
+  <si>
+    <t>版数</t>
+    <rPh sb="0" eb="2">
+      <t>ハンスウ</t>
+    </rPh>
+    <phoneticPr fontId="50"/>
+  </si>
+  <si>
+    <t>変更日</t>
+    <rPh sb="0" eb="3">
+      <t>ヘンコウビ</t>
+    </rPh>
+    <phoneticPr fontId="50"/>
+  </si>
+  <si>
+    <t>区分</t>
+    <rPh sb="0" eb="2">
+      <t>クブン</t>
+    </rPh>
+    <phoneticPr fontId="50"/>
+  </si>
+  <si>
+    <t>変更箇所</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カショ</t>
+    </rPh>
+    <phoneticPr fontId="50"/>
+  </si>
+  <si>
+    <t>変更内容</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="50"/>
+  </si>
+  <si>
+    <t>担当者</t>
+    <rPh sb="0" eb="3">
+      <t>タントウシャ</t>
+    </rPh>
+    <phoneticPr fontId="50"/>
+  </si>
+  <si>
+    <t>頁</t>
+    <rPh sb="0" eb="1">
+      <t>ページ</t>
+    </rPh>
+    <phoneticPr fontId="50"/>
+  </si>
+  <si>
+    <t>項番</t>
+    <rPh sb="0" eb="1">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>バン</t>
+    </rPh>
+    <phoneticPr fontId="50"/>
+  </si>
+  <si>
+    <t>1.0</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>20XX/XX/XX</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>新規</t>
+    <rPh sb="0" eb="2">
+      <t>シンキ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>新規作成</t>
+    <rPh sb="0" eb="2">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>TISXXX</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>目次（１／１）</t>
+  </si>
+  <si>
+    <t>1.はじめに</t>
+  </si>
+  <si>
+    <t>1.1.本書の目的</t>
+  </si>
+  <si>
+    <t>1.2.本書の位置付け</t>
+  </si>
+  <si>
+    <t>1.3.関連文書</t>
+  </si>
+  <si>
+    <t>1.4.本書におけるJakarta EE仕様への読み替えについて</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>2.全体概要</t>
+  </si>
+  <si>
+    <t>2.1.アプリケーション全体図</t>
+  </si>
+  <si>
+    <t>2.2.ソフトウェア構成</t>
+  </si>
+  <si>
+    <t>2.3.アプリケーション・アーキテクチャ</t>
+  </si>
+  <si>
+    <t>2.4.ソフトウェアのバージョン</t>
+  </si>
+  <si>
+    <t>2.4.1.ソフトウェアのバージョン</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>3.画面処理方式</t>
+  </si>
+  <si>
+    <t>3.1.同期処理方式</t>
+  </si>
+  <si>
+    <t>3.1.1.処理方式概要</t>
+  </si>
+  <si>
+    <t>3.1.2.HTTPメソッドの使い分け</t>
+  </si>
+  <si>
+    <t>3.1.3.ブラウザキャッシュ制御</t>
+  </si>
+  <si>
+    <t>3.1.4.オートコンプリート</t>
+  </si>
+  <si>
+    <t>3.1.5.二重サブミット防止</t>
+  </si>
+  <si>
+    <t>3.1.6.データの保持</t>
+  </si>
+  <si>
+    <t>3.1.7.開閉局</t>
+  </si>
+  <si>
+    <t>3.1.8.エラー処理</t>
+  </si>
+  <si>
+    <t>3.1.9.URL設計</t>
+  </si>
+  <si>
+    <t>3.1.10.コンテンツ更新</t>
+  </si>
+  <si>
+    <t>3.1.11.ウィルス対策</t>
+  </si>
+  <si>
+    <t>3.1.12.複数ウィンドウ/タブの同時操作時の挙動</t>
+  </si>
+  <si>
+    <t>3.2.非同期処理方式</t>
+  </si>
+  <si>
+    <t>3.2.1.非同期処理方式概要</t>
+  </si>
+  <si>
+    <t>3.2.2.非同期処理方式詳細</t>
+  </si>
+  <si>
+    <t>3.2.3.非同期処理のエラー時対応</t>
+  </si>
+  <si>
+    <t>4.バッチ処理方式</t>
+  </si>
+  <si>
+    <t>4.1.都度起動バッチ</t>
+  </si>
+  <si>
+    <t>4.1.1.処理方式概要</t>
+  </si>
+  <si>
+    <t>4.1.2.処理制御</t>
+  </si>
+  <si>
+    <t>4.1.3.基本的な処理シーケンス</t>
+  </si>
+  <si>
+    <t>4.1.4.コミット間隔</t>
+  </si>
+  <si>
+    <t>4.1.5.0件データ処理</t>
+  </si>
+  <si>
+    <t>4.1.6.処理済みデータの設定</t>
+  </si>
+  <si>
+    <t>4.1.7.エラー処理</t>
+  </si>
+  <si>
+    <t>4.2.常駐バッチ</t>
+  </si>
+  <si>
+    <t>4.2.1.処理方式概要</t>
+  </si>
+  <si>
+    <t>4.2.2.処理制御</t>
+  </si>
+  <si>
+    <t>4.2.3.コミット間隔</t>
+  </si>
+  <si>
+    <t>4.2.4.エラー処理</t>
+  </si>
+  <si>
+    <t>5.入力処理方式</t>
+  </si>
+  <si>
+    <t>5.1.ファイル転送(集信)</t>
+  </si>
+  <si>
+    <t>5.1.1.処理方式概要</t>
+  </si>
+  <si>
+    <t>5.1.2.処理フロー</t>
+  </si>
+  <si>
+    <t>5.1.3.基本構造・責務配置</t>
+  </si>
+  <si>
+    <t>5.1.4.開閉局</t>
+  </si>
+  <si>
+    <t>5.1.5.入力値精査</t>
+  </si>
+  <si>
+    <t>5.1.6.エラー処理</t>
+  </si>
+  <si>
+    <t>5.1.7.リカバリ方法</t>
+  </si>
+  <si>
+    <t>5.2.REST</t>
+  </si>
+  <si>
+    <t>5.2.1.処理方式概要</t>
+  </si>
+  <si>
+    <t>5.2.2.URL設計</t>
+  </si>
+  <si>
+    <t>5.2.3.データの保持</t>
+  </si>
+  <si>
+    <t>5.2.4.エラー処理</t>
+  </si>
+  <si>
+    <t>5.2.5.データフォーマット</t>
+  </si>
+  <si>
+    <t>5.2.6.ページング</t>
+  </si>
+  <si>
+    <t>5.2.7.CORS</t>
+  </si>
+  <si>
+    <t>5.2.8.CSRF</t>
+  </si>
+  <si>
+    <t>5.2.9.キャッシュ制御</t>
+  </si>
+  <si>
+    <t>5.2.10.Cookie</t>
+  </si>
+  <si>
+    <t>5.2.11.開閉局</t>
+  </si>
+  <si>
+    <t>6.出力処理方式</t>
+  </si>
+  <si>
+    <t>6.1.メッセージ仕向け(REST)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>6.1.1.メッセージ仕向け（HTTP/HTTPS）の機能概要</t>
+  </si>
+  <si>
+    <t>6.1.2.メッセージ仕向け（HTTP/HTTPS）の方法</t>
+  </si>
+  <si>
+    <t>6.1.3.メッセージ仕向け（HTTP/HTTPS）機能詳細</t>
+  </si>
+  <si>
+    <t>6.2.ファイル転送(配信)</t>
+  </si>
+  <si>
+    <t>6.2.1.処理方式概要</t>
+  </si>
+  <si>
+    <t>6.2.2.処理フロー</t>
+  </si>
+  <si>
+    <t>6.2.3.基本構造・責務配置</t>
+  </si>
+  <si>
+    <t>6.2.4.開閉局</t>
+  </si>
+  <si>
+    <t>6.2.5.エラー処理</t>
+  </si>
+  <si>
+    <t>6.2.6.リカバリ方法</t>
+  </si>
+  <si>
+    <t>6.3.メール送信</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>6.3.1.処理方式概要</t>
+  </si>
+  <si>
+    <t>6.3.2.メール送信方式</t>
+  </si>
+  <si>
+    <t>6.3.3.メールテンプレート</t>
+  </si>
+  <si>
+    <t>6.3.4.メールフォーマット</t>
+  </si>
+  <si>
+    <t>6.3.5.エラー処理</t>
+  </si>
+  <si>
+    <t>6.3.6.文字コード</t>
+  </si>
+  <si>
+    <t>6.3.7.送信履歴</t>
+  </si>
+  <si>
+    <t>6.3.8.メール送信のパターン</t>
+  </si>
+  <si>
+    <t>7.処理方式共通</t>
+  </si>
+  <si>
+    <t>7.1.入力値精査</t>
+  </si>
+  <si>
+    <t>7.1.1.  入力値精査処理方式の選択</t>
+  </si>
+  <si>
+    <t>7.1.2.  入力値精査の種類と対象</t>
+  </si>
+  <si>
+    <t>7.1.2.  単項目精査、項目間精査およびFormで完結しない精査の実現方式</t>
+  </si>
+  <si>
+    <t>7.2.文字コード</t>
+  </si>
+  <si>
+    <t>7.2.1.基本方針</t>
+  </si>
+  <si>
+    <t>7.2.2.システムで使用する文字コード</t>
+  </si>
+  <si>
+    <t>7.2.3.文字コード変換方式</t>
+  </si>
+  <si>
+    <t>7.3.DBアクセス処理</t>
+  </si>
+  <si>
+    <t>7.3.1.コネクション</t>
+  </si>
+  <si>
+    <t>7.3.2.データベース接続</t>
+  </si>
+  <si>
+    <t>7.3.3.SQL文の生成</t>
+  </si>
+  <si>
+    <t>7.3.4.トランザクション制御</t>
+  </si>
+  <si>
+    <t>7.4.ファイルアクセス処理</t>
+  </si>
+  <si>
+    <t>7.4.1.ファイルアクセス処理概要</t>
+  </si>
+  <si>
+    <t>7.4.2.データ入出力</t>
+  </si>
+  <si>
+    <t>7.4.3.ファイルクリーニング</t>
+  </si>
+  <si>
+    <t>7.4.4.クリーニングジョブ</t>
+  </si>
+  <si>
+    <t>7.5.認証・認可</t>
+  </si>
+  <si>
+    <t>7.5.1.認証</t>
+  </si>
+  <si>
+    <t>7.5.2.認可</t>
+  </si>
+  <si>
+    <t>7.5.3.認証・認可の管理運用</t>
+  </si>
+  <si>
+    <t>7.6.メッセージ管理方式</t>
+  </si>
+  <si>
+    <t>7.6.1.基本方針</t>
+  </si>
+  <si>
+    <t>7.6.2.メッセージのロード方式</t>
+  </si>
+  <si>
+    <t>7.7.コード管理方式</t>
+  </si>
+  <si>
+    <t>7.7.1.基本方針</t>
+  </si>
+  <si>
+    <t>7.7.2.コードのロード方式</t>
+  </si>
+  <si>
+    <t>7.8.採番方式</t>
+  </si>
+  <si>
+    <t>7.8.1.基本方針</t>
+  </si>
+  <si>
+    <t>7.8.2.値のリセット方法</t>
+  </si>
+  <si>
+    <t>7.8.3.採番処理の実装方針</t>
+  </si>
+  <si>
+    <t>7.9.日付・時刻処理方式</t>
+  </si>
+  <si>
+    <t>7.9.1.基本概念</t>
+  </si>
+  <si>
+    <t>7.9.2.業務日付</t>
+  </si>
+  <si>
+    <t>7.9.3.システム日時</t>
+  </si>
+  <si>
+    <t>7.10.ファイル管理</t>
+  </si>
+  <si>
+    <t>7.10.1.ファイル管理概要</t>
+  </si>
+  <si>
+    <t>7.10.2.ファイル管理詳細</t>
+  </si>
+  <si>
+    <t>7.11.暗号化・ハッシュ化</t>
+  </si>
+  <si>
+    <t>7.11.1.暗号化</t>
+  </si>
+  <si>
+    <t>7.11.2.項目暗号化</t>
   </si>
   <si>
     <t>7.12.負荷分散</t>
@@ -311,235 +620,22 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>2.1.アプリケーション全体図</t>
-  </si>
-  <si>
-    <t>2.2.ソフトウェア構成</t>
-  </si>
-  <si>
-    <t>2.3.アプリケーション・アーキテクチャ</t>
-  </si>
-  <si>
-    <t>2.4.ソフトウェアのバージョン</t>
-  </si>
-  <si>
-    <t>3.1.1.処理方式概要</t>
-  </si>
-  <si>
-    <t>3.1.2.HTTPメソッドの使い分け</t>
-  </si>
-  <si>
-    <t>3.1.3.ブラウザキャッシュ制御</t>
-  </si>
-  <si>
-    <t>3.1.4.オートコンプリート</t>
-  </si>
-  <si>
-    <t>3.2.1.非同期処理方式概要</t>
-  </si>
-  <si>
-    <t>3.2.2.非同期処理方式詳細</t>
-  </si>
-  <si>
-    <t>3.2.3.非同期処理のエラー時対応</t>
-  </si>
-  <si>
-    <t>4.1.1.処理方式概要</t>
-  </si>
-  <si>
-    <t>4.1.2.処理制御</t>
-  </si>
-  <si>
-    <t>4.1.3.基本的な処理シーケンス</t>
-  </si>
-  <si>
-    <t>4.1.4.コミット間隔</t>
-  </si>
-  <si>
-    <t>4.1.5.0件データ処理</t>
-  </si>
-  <si>
-    <t>4.1.6.処理済みデータの設定</t>
-  </si>
-  <si>
-    <t>4.1.7.エラー処理</t>
-  </si>
-  <si>
-    <t>4.2.1.処理方式概要</t>
-  </si>
-  <si>
-    <t>4.2.2.処理制御</t>
-  </si>
-  <si>
-    <t>4.2.3.コミット間隔</t>
-  </si>
-  <si>
-    <t>4.2.4.エラー処理</t>
-  </si>
-  <si>
-    <t>5.1.1.処理方式概要</t>
-  </si>
-  <si>
-    <t>5.1.2.処理フロー</t>
-  </si>
-  <si>
-    <t>5.1.3.基本構造・責務配置</t>
-  </si>
-  <si>
-    <t>5.1.4.開閉局</t>
-  </si>
-  <si>
-    <t>5.1.5.入力値精査</t>
-  </si>
-  <si>
-    <t>5.1.6.エラー処理</t>
-  </si>
-  <si>
-    <t>5.1.7.リカバリ方法</t>
-  </si>
-  <si>
-    <t>6.1.1.メッセージ仕向け（HTTP/HTTPS）の機能概要</t>
-  </si>
-  <si>
-    <t>6.1.2.メッセージ仕向け（HTTP/HTTPS）の方法</t>
-  </si>
-  <si>
-    <t>6.1.3.メッセージ仕向け（HTTP/HTTPS）機能詳細</t>
-  </si>
-  <si>
-    <t>6.2.1.処理方式概要</t>
-  </si>
-  <si>
-    <t>6.2.2.処理フロー</t>
-  </si>
-  <si>
-    <t>6.2.3.基本構造・責務配置</t>
-  </si>
-  <si>
-    <t>6.2.4.開閉局</t>
-  </si>
-  <si>
-    <t>6.2.5.エラー処理</t>
-  </si>
-  <si>
-    <t>6.2.6.リカバリ方法</t>
-  </si>
-  <si>
-    <t>6.3.1.処理方式概要</t>
-  </si>
-  <si>
-    <t>6.3.2.メール送信方式</t>
-  </si>
-  <si>
-    <t>6.3.3.メールテンプレート</t>
-  </si>
-  <si>
-    <t>6.3.4.メールフォーマット</t>
-  </si>
-  <si>
-    <t>6.3.5.エラー処理</t>
-  </si>
-  <si>
-    <t>6.3.6.文字コード</t>
-  </si>
-  <si>
-    <t>6.3.7.送信履歴</t>
-  </si>
-  <si>
-    <t>6.3.8.メール送信のパターン</t>
-  </si>
-  <si>
-    <t>7.1.1.  入力値精査処理方式の選択</t>
-  </si>
-  <si>
-    <t>7.1.2.  入力値精査の種類と対象</t>
-  </si>
-  <si>
-    <t>7.1.2.  単項目精査、項目間精査およびFormで完結しない精査の実現方式</t>
-  </si>
-  <si>
-    <t>7.2.1.基本方針</t>
-  </si>
-  <si>
-    <t>7.2.2.システムで使用する文字コード</t>
-  </si>
-  <si>
-    <t>7.2.3.文字コード変換方式</t>
-  </si>
-  <si>
-    <t>7.3.1.コネクション</t>
-  </si>
-  <si>
-    <t>7.3.2.データベース接続</t>
-  </si>
-  <si>
-    <t>7.3.3.SQL文の生成</t>
-  </si>
-  <si>
-    <t>7.3.4.トランザクション制御</t>
-  </si>
-  <si>
-    <t>7.4.1.ファイルアクセス処理概要</t>
-  </si>
-  <si>
-    <t>7.4.2.データ入出力</t>
-  </si>
-  <si>
-    <t>7.4.3.ファイルクリーニング</t>
-  </si>
-  <si>
-    <t>7.4.4.クリーニングジョブ</t>
-  </si>
-  <si>
-    <t>7.5.1.認証</t>
-  </si>
-  <si>
-    <t>7.5.2.認可</t>
-  </si>
-  <si>
-    <t>7.5.3.認証・認可の管理運用</t>
-  </si>
-  <si>
-    <t>7.6.1.基本方針</t>
-  </si>
-  <si>
-    <t>7.6.2.メッセージのロード方式</t>
-  </si>
-  <si>
-    <t>7.7.1.基本方針</t>
-  </si>
-  <si>
-    <t>7.7.2.コードのロード方式</t>
-  </si>
-  <si>
-    <t>7.8.1.基本方針</t>
-  </si>
-  <si>
-    <t>7.8.2.値のリセット方法</t>
-  </si>
-  <si>
-    <t>7.8.3.採番処理の実装方針</t>
-  </si>
-  <si>
-    <t>7.9.1.基本概念</t>
-  </si>
-  <si>
-    <t>7.9.2.業務日付</t>
-  </si>
-  <si>
-    <t>7.9.3.システム日時</t>
-  </si>
-  <si>
-    <t>7.10.1.ファイル管理概要</t>
-  </si>
-  <si>
-    <t>7.10.2.ファイル管理詳細</t>
-  </si>
-  <si>
-    <t>7.11.1.暗号化</t>
-  </si>
-  <si>
-    <t>7.11.2.項目暗号化</t>
+    <t>7.12.1.負荷分散方針</t>
+    <rPh sb="7" eb="11">
+      <t>フカブンサン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ホウシン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>7.12.2.ヘルスチェック</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>7.13.ログ</t>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>7.13.1.ログ定義</t>
@@ -558,30 +654,6 @@
   </si>
   <si>
     <t>7.13.6.シェルスクリプトのログ</t>
-  </si>
-  <si>
-    <t>3.1.5.二重サブミット防止</t>
-  </si>
-  <si>
-    <t>3.1.6.データの保持</t>
-  </si>
-  <si>
-    <t>3.1.7.開閉局</t>
-  </si>
-  <si>
-    <t>3.1.8.エラー処理</t>
-  </si>
-  <si>
-    <t>3.1.9.URL設計</t>
-  </si>
-  <si>
-    <t>3.1.10.コンテンツ更新</t>
-  </si>
-  <si>
-    <t>3.1.11.ウィルス対策</t>
-  </si>
-  <si>
-    <t>3.1.12.複数ウィンドウ/タブの同時操作時の挙動</t>
   </si>
 </sst>
 </file>
@@ -3813,7 +3885,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3825,7 +3897,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -3855,19 +3927,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="24" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3879,11 +3948,11 @@
     <xf numFmtId="0" fontId="44" fillId="24" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="6" applyFont="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="24" borderId="23" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3895,30 +3964,27 @@
     <xf numFmtId="0" fontId="44" fillId="24" borderId="25" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="24" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="24" borderId="2" xfId="6" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="44" fillId="24" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="24" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="24" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="24" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="24" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="44" fillId="24" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="44" fillId="24" borderId="2" xfId="6" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="44" fillId="24" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="44" fillId="24" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="44" fillId="24" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="44" fillId="24" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="44" fillId="24" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3940,8 +4006,7 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3951,16 +4016,14 @@
     <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3997,10 +4060,10 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4042,56 +4105,47 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="48" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="48" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="48" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="48" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="48" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="48" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4162,40 +4216,40 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="44" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="44" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="44" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="44" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="44" fillId="0" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="44" fillId="0" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="48" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="48" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="48" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="48" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="23" xfId="559" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="23" xfId="559" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="24" xfId="559" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="24" xfId="559" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="25" xfId="559" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="25" xfId="559" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="6" xfId="559" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="6" xfId="559" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="4" xfId="559" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="4" xfId="559" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="5" xfId="559" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="5" xfId="559" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="44" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6298,7 +6352,7 @@
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="7" t="s">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
@@ -6374,7 +6428,7 @@
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="8" t="s">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
@@ -6742,11 +6796,11 @@
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
-      <c r="O35" s="16"/>
+      <c r="O35" s="1"/>
       <c r="P35" s="15"/>
-      <c r="Q35" s="16"/>
+      <c r="Q35" s="1"/>
       <c r="R35" s="15"/>
-      <c r="S35" s="17"/>
+      <c r="S35" s="16"/>
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
@@ -6779,11 +6833,11 @@
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
-      <c r="O36" s="16"/>
+      <c r="O36" s="1"/>
       <c r="P36" s="15"/>
-      <c r="Q36" s="16"/>
+      <c r="Q36" s="1"/>
       <c r="R36" s="15"/>
-      <c r="S36" s="16"/>
+      <c r="S36" s="1"/>
       <c r="T36" s="1"/>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
@@ -6806,7 +6860,7 @@
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="18"/>
+      <c r="E37" s="17"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
@@ -6819,7 +6873,7 @@
       <c r="O37" s="15"/>
       <c r="P37" s="15"/>
       <c r="R37" s="15"/>
-      <c r="S37" s="19"/>
+      <c r="S37" s="18"/>
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
@@ -7361,1246 +7415,1246 @@
   <dimension ref="A1:AN34"/>
   <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="4.83203125" style="45"/>
+    <col min="1" max="16384" width="4.83203125" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="25" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="122" t="s">
+    <row r="1" spans="1:40" s="24" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="114" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="117" t="s">
+        <v>5</v>
+      </c>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
+      <c r="V1" s="118"/>
+      <c r="W1" s="118"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z1" s="21"/>
+      <c r="AA1" s="120"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="121"/>
+      <c r="AE1" s="122"/>
+      <c r="AF1" s="123"/>
+      <c r="AG1" s="124"/>
+      <c r="AH1" s="124"/>
+      <c r="AI1" s="125"/>
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="22"/>
+      <c r="AL1" s="22"/>
+      <c r="AM1" s="22"/>
+      <c r="AN1" s="23"/>
+    </row>
+    <row r="2" spans="1:40" s="24" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="115"/>
+      <c r="M2" s="115"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="126" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" s="127"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
+      <c r="U2" s="127"/>
+      <c r="V2" s="127"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="128"/>
+      <c r="Y2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z2" s="21"/>
+      <c r="AA2" s="120"/>
+      <c r="AB2" s="121"/>
+      <c r="AC2" s="121"/>
+      <c r="AD2" s="121"/>
+      <c r="AE2" s="122"/>
+      <c r="AF2" s="132"/>
+      <c r="AG2" s="133"/>
+      <c r="AH2" s="133"/>
+      <c r="AI2" s="134"/>
+      <c r="AJ2" s="22"/>
+      <c r="AK2" s="22"/>
+      <c r="AL2" s="22"/>
+      <c r="AM2" s="22"/>
+      <c r="AN2" s="22"/>
+    </row>
+    <row r="3" spans="1:40" s="24" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="29"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="136"/>
+      <c r="M3" s="136"/>
+      <c r="N3" s="137"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="129"/>
+      <c r="R3" s="130"/>
+      <c r="S3" s="130"/>
+      <c r="T3" s="130"/>
+      <c r="U3" s="130"/>
+      <c r="V3" s="130"/>
+      <c r="W3" s="130"/>
+      <c r="X3" s="131"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="34"/>
+      <c r="AA3" s="120"/>
+      <c r="AB3" s="121"/>
+      <c r="AC3" s="121"/>
+      <c r="AD3" s="121"/>
+      <c r="AE3" s="122"/>
+      <c r="AF3" s="138"/>
+      <c r="AG3" s="139"/>
+      <c r="AH3" s="139"/>
+      <c r="AI3" s="140"/>
+      <c r="AJ3" s="22"/>
+      <c r="AK3" s="22"/>
+      <c r="AL3" s="22"/>
+      <c r="AM3" s="22"/>
+      <c r="AN3" s="22"/>
+    </row>
+    <row r="5" spans="1:40" s="24" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N5" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA5" s="36"/>
+      <c r="AB5" s="36"/>
+      <c r="AC5" s="37"/>
+      <c r="AD5" s="38"/>
+      <c r="AE5" s="38"/>
+      <c r="AF5" s="38"/>
+      <c r="AG5" s="36"/>
+      <c r="AH5" s="36"/>
+      <c r="AI5" s="36"/>
+    </row>
+    <row r="6" spans="1:40" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N6" s="35"/>
+      <c r="AA6" s="36"/>
+      <c r="AB6" s="36"/>
+      <c r="AC6" s="37"/>
+      <c r="AD6" s="38"/>
+      <c r="AE6" s="38"/>
+      <c r="AF6" s="38"/>
+      <c r="AG6" s="36"/>
+      <c r="AH6" s="36"/>
+      <c r="AI6" s="36"/>
+    </row>
+    <row r="7" spans="1:40" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="100" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="102" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="103"/>
+      <c r="D7" s="102" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="106"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="102" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="106"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="108" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="109"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="110"/>
+      <c r="P7" s="102" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q7" s="106"/>
+      <c r="R7" s="106"/>
+      <c r="S7" s="106"/>
+      <c r="T7" s="106"/>
+      <c r="U7" s="106"/>
+      <c r="V7" s="106"/>
+      <c r="W7" s="106"/>
+      <c r="X7" s="106"/>
+      <c r="Y7" s="106"/>
+      <c r="Z7" s="106"/>
+      <c r="AA7" s="106"/>
+      <c r="AB7" s="106"/>
+      <c r="AC7" s="106"/>
+      <c r="AD7" s="103"/>
+      <c r="AE7" s="102" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF7" s="106"/>
+      <c r="AG7" s="106"/>
+      <c r="AH7" s="106"/>
+      <c r="AI7" s="103"/>
+    </row>
+    <row r="8" spans="1:40" s="39" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="101"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="111" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="112"/>
+      <c r="L8" s="111" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="113"/>
+      <c r="P8" s="104"/>
+      <c r="Q8" s="107"/>
+      <c r="R8" s="107"/>
+      <c r="S8" s="107"/>
+      <c r="T8" s="107"/>
+      <c r="U8" s="107"/>
+      <c r="V8" s="107"/>
+      <c r="W8" s="107"/>
+      <c r="X8" s="107"/>
+      <c r="Y8" s="107"/>
+      <c r="Z8" s="107"/>
+      <c r="AA8" s="107"/>
+      <c r="AB8" s="107"/>
+      <c r="AC8" s="107"/>
+      <c r="AD8" s="105"/>
+      <c r="AE8" s="104"/>
+      <c r="AF8" s="107"/>
+      <c r="AG8" s="107"/>
+      <c r="AH8" s="107"/>
+      <c r="AI8" s="105"/>
+    </row>
+    <row r="9" spans="1:40" s="39" customFormat="1" ht="12" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="40">
         <v>1</v>
       </c>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="123"/>
-      <c r="K1" s="123"/>
-      <c r="L1" s="123"/>
-      <c r="M1" s="123"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="125" t="s">
-        <v>3</v>
-      </c>
-      <c r="R1" s="126"/>
-      <c r="S1" s="126"/>
-      <c r="T1" s="126"/>
-      <c r="U1" s="126"/>
-      <c r="V1" s="126"/>
-      <c r="W1" s="126"/>
-      <c r="X1" s="127"/>
-      <c r="Y1" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="128"/>
-      <c r="AB1" s="129"/>
-      <c r="AC1" s="129"/>
-      <c r="AD1" s="129"/>
-      <c r="AE1" s="130"/>
-      <c r="AF1" s="131"/>
-      <c r="AG1" s="132"/>
-      <c r="AH1" s="132"/>
-      <c r="AI1" s="133"/>
-      <c r="AJ1" s="23"/>
-      <c r="AK1" s="23"/>
-      <c r="AL1" s="23"/>
-      <c r="AM1" s="23"/>
-      <c r="AN1" s="24"/>
-    </row>
-    <row r="2" spans="1:40" s="25" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="122"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="123"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="123"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="134" t="s">
-        <v>7</v>
-      </c>
-      <c r="R2" s="135"/>
-      <c r="S2" s="135"/>
-      <c r="T2" s="135"/>
-      <c r="U2" s="135"/>
-      <c r="V2" s="135"/>
-      <c r="W2" s="135"/>
-      <c r="X2" s="136"/>
-      <c r="Y2" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z2" s="22"/>
-      <c r="AA2" s="128"/>
-      <c r="AB2" s="129"/>
-      <c r="AC2" s="129"/>
-      <c r="AD2" s="129"/>
-      <c r="AE2" s="130"/>
-      <c r="AF2" s="140"/>
-      <c r="AG2" s="141"/>
-      <c r="AH2" s="141"/>
-      <c r="AI2" s="142"/>
-      <c r="AJ2" s="23"/>
-      <c r="AK2" s="23"/>
-      <c r="AL2" s="23"/>
-      <c r="AM2" s="23"/>
-      <c r="AN2" s="23"/>
-    </row>
-    <row r="3" spans="1:40" s="25" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="144"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
-      <c r="K3" s="144"/>
-      <c r="L3" s="144"/>
-      <c r="M3" s="144"/>
-      <c r="N3" s="145"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="137"/>
-      <c r="R3" s="138"/>
-      <c r="S3" s="138"/>
-      <c r="T3" s="138"/>
-      <c r="U3" s="138"/>
-      <c r="V3" s="138"/>
-      <c r="W3" s="138"/>
-      <c r="X3" s="139"/>
-      <c r="Y3" s="33"/>
-      <c r="Z3" s="35"/>
-      <c r="AA3" s="128"/>
-      <c r="AB3" s="129"/>
-      <c r="AC3" s="129"/>
-      <c r="AD3" s="129"/>
-      <c r="AE3" s="130"/>
-      <c r="AF3" s="146"/>
-      <c r="AG3" s="147"/>
-      <c r="AH3" s="147"/>
-      <c r="AI3" s="148"/>
-      <c r="AJ3" s="23"/>
-      <c r="AK3" s="23"/>
-      <c r="AL3" s="23"/>
-      <c r="AM3" s="23"/>
-      <c r="AN3" s="23"/>
-    </row>
-    <row r="5" spans="1:40" s="36" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="N5" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="39"/>
-      <c r="AD5" s="40"/>
-      <c r="AE5" s="40"/>
-      <c r="AF5" s="40"/>
-      <c r="AG5" s="38"/>
-      <c r="AH5" s="38"/>
-      <c r="AI5" s="38"/>
-    </row>
-    <row r="6" spans="1:40" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="N6" s="37"/>
-      <c r="AA6" s="38"/>
-      <c r="AB6" s="38"/>
-      <c r="AC6" s="39"/>
-      <c r="AD6" s="40"/>
-      <c r="AE6" s="40"/>
-      <c r="AF6" s="40"/>
-      <c r="AG6" s="38"/>
-      <c r="AH6" s="38"/>
-      <c r="AI6" s="38"/>
-    </row>
-    <row r="7" spans="1:40" s="41" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="108" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="110" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="111"/>
-      <c r="D7" s="110" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="114"/>
-      <c r="F7" s="111"/>
-      <c r="G7" s="110" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="114"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="116" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" s="117"/>
-      <c r="L7" s="117"/>
-      <c r="M7" s="117"/>
-      <c r="N7" s="117"/>
-      <c r="O7" s="118"/>
-      <c r="P7" s="110" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q7" s="114"/>
-      <c r="R7" s="114"/>
-      <c r="S7" s="114"/>
-      <c r="T7" s="114"/>
-      <c r="U7" s="114"/>
-      <c r="V7" s="114"/>
-      <c r="W7" s="114"/>
-      <c r="X7" s="114"/>
-      <c r="Y7" s="114"/>
-      <c r="Z7" s="114"/>
-      <c r="AA7" s="114"/>
-      <c r="AB7" s="114"/>
-      <c r="AC7" s="114"/>
-      <c r="AD7" s="111"/>
-      <c r="AE7" s="110" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF7" s="114"/>
-      <c r="AG7" s="114"/>
-      <c r="AH7" s="114"/>
-      <c r="AI7" s="111"/>
-    </row>
-    <row r="8" spans="1:40" s="41" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="109"/>
-      <c r="B8" s="112"/>
-      <c r="C8" s="113"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="115"/>
-      <c r="F8" s="113"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="115"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="119" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="120"/>
-      <c r="L8" s="119" t="s">
-        <v>19</v>
-      </c>
-      <c r="M8" s="120"/>
-      <c r="N8" s="120"/>
-      <c r="O8" s="121"/>
-      <c r="P8" s="112"/>
-      <c r="Q8" s="115"/>
-      <c r="R8" s="115"/>
-      <c r="S8" s="115"/>
-      <c r="T8" s="115"/>
-      <c r="U8" s="115"/>
-      <c r="V8" s="115"/>
-      <c r="W8" s="115"/>
-      <c r="X8" s="115"/>
-      <c r="Y8" s="115"/>
-      <c r="Z8" s="115"/>
-      <c r="AA8" s="115"/>
-      <c r="AB8" s="115"/>
-      <c r="AC8" s="115"/>
-      <c r="AD8" s="113"/>
-      <c r="AE8" s="112"/>
-      <c r="AF8" s="115"/>
-      <c r="AG8" s="115"/>
-      <c r="AH8" s="115"/>
-      <c r="AI8" s="113"/>
-    </row>
-    <row r="9" spans="1:40" s="41" customFormat="1" ht="12" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="42">
-        <v>1</v>
-      </c>
-      <c r="B9" s="94" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="95"/>
-      <c r="D9" s="96" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="97"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="99" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="100"/>
-      <c r="I9" s="101"/>
-      <c r="J9" s="102"/>
-      <c r="K9" s="103"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="104"/>
-      <c r="N9" s="104"/>
-      <c r="O9" s="103"/>
-      <c r="P9" s="105" t="s">
+      <c r="B9" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="Q9" s="106"/>
-      <c r="R9" s="106"/>
-      <c r="S9" s="106"/>
-      <c r="T9" s="106"/>
-      <c r="U9" s="106"/>
-      <c r="V9" s="106"/>
-      <c r="W9" s="106"/>
-      <c r="X9" s="106"/>
-      <c r="Y9" s="106"/>
-      <c r="Z9" s="106"/>
-      <c r="AA9" s="106"/>
-      <c r="AB9" s="106"/>
-      <c r="AC9" s="106"/>
-      <c r="AD9" s="107"/>
-      <c r="AE9" s="91" t="s">
+      <c r="C9" s="90"/>
+      <c r="D9" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="AF9" s="92"/>
-      <c r="AG9" s="92"/>
-      <c r="AH9" s="92"/>
-      <c r="AI9" s="93"/>
-    </row>
-    <row r="10" spans="1:40" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="43"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="89"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="65"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="90"/>
-      <c r="M10" s="62"/>
-      <c r="N10" s="62"/>
-      <c r="O10" s="63"/>
-      <c r="P10" s="70"/>
-      <c r="Q10" s="71"/>
-      <c r="R10" s="71"/>
-      <c r="S10" s="71"/>
-      <c r="T10" s="71"/>
-      <c r="U10" s="71"/>
-      <c r="V10" s="71"/>
-      <c r="W10" s="71"/>
-      <c r="X10" s="71"/>
-      <c r="Y10" s="71"/>
-      <c r="Z10" s="71"/>
-      <c r="AA10" s="71"/>
-      <c r="AB10" s="71"/>
-      <c r="AC10" s="71"/>
-      <c r="AD10" s="72"/>
-      <c r="AE10" s="61"/>
-      <c r="AF10" s="62"/>
-      <c r="AG10" s="62"/>
-      <c r="AH10" s="62"/>
-      <c r="AI10" s="63"/>
-    </row>
-    <row r="11" spans="1:40" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="43"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="89"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="90"/>
-      <c r="M11" s="62"/>
-      <c r="N11" s="62"/>
-      <c r="O11" s="63"/>
-      <c r="P11" s="70"/>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="71"/>
-      <c r="S11" s="71"/>
-      <c r="T11" s="71"/>
-      <c r="U11" s="71"/>
-      <c r="V11" s="71"/>
-      <c r="W11" s="71"/>
-      <c r="X11" s="71"/>
-      <c r="Y11" s="71"/>
-      <c r="Z11" s="71"/>
-      <c r="AA11" s="71"/>
-      <c r="AB11" s="71"/>
-      <c r="AC11" s="71"/>
-      <c r="AD11" s="72"/>
-      <c r="AE11" s="61"/>
-      <c r="AF11" s="62"/>
-      <c r="AG11" s="62"/>
-      <c r="AH11" s="62"/>
-      <c r="AI11" s="63"/>
-    </row>
-    <row r="12" spans="1:40" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="44"/>
-      <c r="B12" s="73"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="80"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="82"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="84"/>
-      <c r="O12" s="82"/>
-      <c r="P12" s="85"/>
-      <c r="Q12" s="86"/>
-      <c r="R12" s="86"/>
-      <c r="S12" s="86"/>
-      <c r="T12" s="86"/>
-      <c r="U12" s="86"/>
-      <c r="V12" s="86"/>
-      <c r="W12" s="86"/>
-      <c r="X12" s="86"/>
-      <c r="Y12" s="86"/>
-      <c r="Z12" s="86"/>
-      <c r="AA12" s="86"/>
-      <c r="AB12" s="86"/>
-      <c r="AC12" s="86"/>
-      <c r="AD12" s="87"/>
-      <c r="AE12" s="81"/>
-      <c r="AF12" s="84"/>
-      <c r="AG12" s="84"/>
-      <c r="AH12" s="84"/>
-      <c r="AI12" s="82"/>
-    </row>
-    <row r="13" spans="1:40" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="43"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="65"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="61"/>
-      <c r="M13" s="62"/>
-      <c r="N13" s="62"/>
-      <c r="O13" s="63"/>
-      <c r="P13" s="70"/>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="71"/>
-      <c r="T13" s="71"/>
-      <c r="U13" s="71"/>
-      <c r="V13" s="71"/>
-      <c r="W13" s="71"/>
-      <c r="X13" s="71"/>
-      <c r="Y13" s="71"/>
-      <c r="Z13" s="71"/>
-      <c r="AA13" s="71"/>
-      <c r="AB13" s="71"/>
-      <c r="AC13" s="71"/>
-      <c r="AD13" s="72"/>
-      <c r="AE13" s="61"/>
-      <c r="AF13" s="62"/>
-      <c r="AG13" s="62"/>
-      <c r="AH13" s="62"/>
-      <c r="AI13" s="63"/>
-    </row>
-    <row r="14" spans="1:40" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="43"/>
-      <c r="B14" s="64"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="63"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="62"/>
-      <c r="N14" s="62"/>
-      <c r="O14" s="63"/>
-      <c r="P14" s="70"/>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="71"/>
-      <c r="S14" s="71"/>
-      <c r="T14" s="71"/>
-      <c r="U14" s="71"/>
-      <c r="V14" s="71"/>
-      <c r="W14" s="71"/>
-      <c r="X14" s="71"/>
-      <c r="Y14" s="71"/>
-      <c r="Z14" s="71"/>
-      <c r="AA14" s="71"/>
-      <c r="AB14" s="71"/>
-      <c r="AC14" s="71"/>
-      <c r="AD14" s="72"/>
-      <c r="AE14" s="61"/>
-      <c r="AF14" s="62"/>
-      <c r="AG14" s="62"/>
-      <c r="AH14" s="62"/>
-      <c r="AI14" s="63"/>
-    </row>
-    <row r="15" spans="1:40" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="43"/>
-      <c r="B15" s="64"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="63"/>
-      <c r="L15" s="61"/>
-      <c r="M15" s="62"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="63"/>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="71"/>
-      <c r="S15" s="71"/>
-      <c r="T15" s="71"/>
-      <c r="U15" s="71"/>
-      <c r="V15" s="71"/>
-      <c r="W15" s="71"/>
-      <c r="X15" s="71"/>
-      <c r="Y15" s="71"/>
-      <c r="Z15" s="71"/>
-      <c r="AA15" s="71"/>
-      <c r="AB15" s="71"/>
-      <c r="AC15" s="71"/>
-      <c r="AD15" s="72"/>
-      <c r="AE15" s="61"/>
-      <c r="AF15" s="62"/>
-      <c r="AG15" s="62"/>
-      <c r="AH15" s="62"/>
-      <c r="AI15" s="63"/>
-    </row>
-    <row r="16" spans="1:40" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="43"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="63"/>
-      <c r="L16" s="61"/>
-      <c r="M16" s="62"/>
-      <c r="N16" s="62"/>
-      <c r="O16" s="63"/>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="71"/>
-      <c r="S16" s="71"/>
-      <c r="T16" s="71"/>
-      <c r="U16" s="71"/>
-      <c r="V16" s="71"/>
-      <c r="W16" s="71"/>
-      <c r="X16" s="71"/>
-      <c r="Y16" s="71"/>
-      <c r="Z16" s="71"/>
-      <c r="AA16" s="71"/>
-      <c r="AB16" s="71"/>
-      <c r="AC16" s="71"/>
-      <c r="AD16" s="72"/>
-      <c r="AE16" s="61"/>
-      <c r="AF16" s="62"/>
-      <c r="AG16" s="62"/>
-      <c r="AH16" s="62"/>
-      <c r="AI16" s="63"/>
-    </row>
-    <row r="17" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="43"/>
-      <c r="B17" s="64"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="67"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="61"/>
-      <c r="K17" s="63"/>
-      <c r="L17" s="61"/>
-      <c r="M17" s="62"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="63"/>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="71"/>
-      <c r="R17" s="71"/>
-      <c r="S17" s="71"/>
-      <c r="T17" s="71"/>
-      <c r="U17" s="71"/>
-      <c r="V17" s="71"/>
-      <c r="W17" s="71"/>
-      <c r="X17" s="71"/>
-      <c r="Y17" s="71"/>
-      <c r="Z17" s="71"/>
-      <c r="AA17" s="71"/>
-      <c r="AB17" s="71"/>
-      <c r="AC17" s="71"/>
-      <c r="AD17" s="72"/>
-      <c r="AE17" s="61"/>
-      <c r="AF17" s="62"/>
-      <c r="AG17" s="62"/>
-      <c r="AH17" s="62"/>
-      <c r="AI17" s="63"/>
-    </row>
-    <row r="18" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="43"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="63"/>
-      <c r="L18" s="61"/>
-      <c r="M18" s="62"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="63"/>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="71"/>
-      <c r="R18" s="71"/>
-      <c r="S18" s="71"/>
-      <c r="T18" s="71"/>
-      <c r="U18" s="71"/>
-      <c r="V18" s="71"/>
-      <c r="W18" s="71"/>
-      <c r="X18" s="71"/>
-      <c r="Y18" s="71"/>
-      <c r="Z18" s="71"/>
-      <c r="AA18" s="71"/>
-      <c r="AB18" s="71"/>
-      <c r="AC18" s="71"/>
-      <c r="AD18" s="72"/>
-      <c r="AE18" s="61"/>
-      <c r="AF18" s="62"/>
-      <c r="AG18" s="62"/>
-      <c r="AH18" s="62"/>
-      <c r="AI18" s="63"/>
-    </row>
-    <row r="19" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="43"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="61"/>
-      <c r="K19" s="63"/>
-      <c r="L19" s="61"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="63"/>
-      <c r="P19" s="70"/>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="71"/>
-      <c r="S19" s="71"/>
-      <c r="T19" s="71"/>
-      <c r="U19" s="71"/>
-      <c r="V19" s="71"/>
-      <c r="W19" s="71"/>
-      <c r="X19" s="71"/>
-      <c r="Y19" s="71"/>
-      <c r="Z19" s="71"/>
-      <c r="AA19" s="71"/>
-      <c r="AB19" s="71"/>
-      <c r="AC19" s="71"/>
-      <c r="AD19" s="72"/>
-      <c r="AE19" s="61"/>
-      <c r="AF19" s="62"/>
-      <c r="AG19" s="62"/>
-      <c r="AH19" s="62"/>
-      <c r="AI19" s="63"/>
-    </row>
-    <row r="20" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="43"/>
-      <c r="B20" s="64"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="63"/>
-      <c r="L20" s="61"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="63"/>
-      <c r="P20" s="70"/>
-      <c r="Q20" s="71"/>
-      <c r="R20" s="71"/>
-      <c r="S20" s="71"/>
-      <c r="T20" s="71"/>
-      <c r="U20" s="71"/>
-      <c r="V20" s="71"/>
-      <c r="W20" s="71"/>
-      <c r="X20" s="71"/>
-      <c r="Y20" s="71"/>
-      <c r="Z20" s="71"/>
-      <c r="AA20" s="71"/>
-      <c r="AB20" s="71"/>
-      <c r="AC20" s="71"/>
-      <c r="AD20" s="72"/>
-      <c r="AE20" s="61"/>
-      <c r="AF20" s="62"/>
-      <c r="AG20" s="62"/>
-      <c r="AH20" s="62"/>
-      <c r="AI20" s="63"/>
-    </row>
-    <row r="21" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="43"/>
-      <c r="B21" s="64"/>
-      <c r="C21" s="65"/>
-      <c r="D21" s="66"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="63"/>
-      <c r="L21" s="61"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="63"/>
-      <c r="P21" s="70"/>
-      <c r="Q21" s="71"/>
-      <c r="R21" s="71"/>
-      <c r="S21" s="71"/>
-      <c r="T21" s="71"/>
-      <c r="U21" s="71"/>
-      <c r="V21" s="71"/>
-      <c r="W21" s="71"/>
-      <c r="X21" s="71"/>
-      <c r="Y21" s="71"/>
-      <c r="Z21" s="71"/>
-      <c r="AA21" s="71"/>
-      <c r="AB21" s="71"/>
-      <c r="AC21" s="71"/>
-      <c r="AD21" s="72"/>
-      <c r="AE21" s="61"/>
-      <c r="AF21" s="62"/>
-      <c r="AG21" s="62"/>
-      <c r="AH21" s="62"/>
-      <c r="AI21" s="63"/>
-    </row>
-    <row r="22" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="43"/>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="61"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="61"/>
-      <c r="M22" s="62"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="63"/>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="71"/>
-      <c r="R22" s="71"/>
-      <c r="S22" s="71"/>
-      <c r="T22" s="71"/>
-      <c r="U22" s="71"/>
-      <c r="V22" s="71"/>
-      <c r="W22" s="71"/>
-      <c r="X22" s="71"/>
-      <c r="Y22" s="71"/>
-      <c r="Z22" s="71"/>
-      <c r="AA22" s="71"/>
-      <c r="AB22" s="71"/>
-      <c r="AC22" s="71"/>
-      <c r="AD22" s="72"/>
-      <c r="AE22" s="61"/>
-      <c r="AF22" s="62"/>
-      <c r="AG22" s="62"/>
-      <c r="AH22" s="62"/>
-      <c r="AI22" s="63"/>
-    </row>
-    <row r="23" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="43"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="61"/>
-      <c r="K23" s="63"/>
-      <c r="L23" s="61"/>
-      <c r="M23" s="62"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="63"/>
-      <c r="P23" s="70"/>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="71"/>
-      <c r="S23" s="71"/>
-      <c r="T23" s="71"/>
-      <c r="U23" s="71"/>
-      <c r="V23" s="71"/>
-      <c r="W23" s="71"/>
-      <c r="X23" s="71"/>
-      <c r="Y23" s="71"/>
-      <c r="Z23" s="71"/>
-      <c r="AA23" s="71"/>
-      <c r="AB23" s="71"/>
-      <c r="AC23" s="71"/>
-      <c r="AD23" s="72"/>
-      <c r="AE23" s="61"/>
-      <c r="AF23" s="62"/>
-      <c r="AG23" s="62"/>
-      <c r="AH23" s="62"/>
-      <c r="AI23" s="63"/>
-    </row>
-    <row r="24" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="43"/>
-      <c r="B24" s="64"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="61"/>
-      <c r="M24" s="62"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="63"/>
-      <c r="P24" s="70"/>
-      <c r="Q24" s="71"/>
-      <c r="R24" s="71"/>
-      <c r="S24" s="71"/>
-      <c r="T24" s="71"/>
-      <c r="U24" s="71"/>
-      <c r="V24" s="71"/>
-      <c r="W24" s="71"/>
-      <c r="X24" s="71"/>
-      <c r="Y24" s="71"/>
-      <c r="Z24" s="71"/>
-      <c r="AA24" s="71"/>
-      <c r="AB24" s="71"/>
-      <c r="AC24" s="71"/>
-      <c r="AD24" s="72"/>
-      <c r="AE24" s="61"/>
-      <c r="AF24" s="62"/>
-      <c r="AG24" s="62"/>
-      <c r="AH24" s="62"/>
-      <c r="AI24" s="63"/>
-    </row>
-    <row r="25" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="43"/>
-      <c r="B25" s="64"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="66"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="63"/>
-      <c r="L25" s="61"/>
-      <c r="M25" s="62"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="63"/>
-      <c r="P25" s="70"/>
-      <c r="Q25" s="71"/>
-      <c r="R25" s="71"/>
-      <c r="S25" s="71"/>
-      <c r="T25" s="71"/>
-      <c r="U25" s="71"/>
-      <c r="V25" s="71"/>
-      <c r="W25" s="71"/>
-      <c r="X25" s="71"/>
-      <c r="Y25" s="71"/>
-      <c r="Z25" s="71"/>
-      <c r="AA25" s="71"/>
-      <c r="AB25" s="71"/>
-      <c r="AC25" s="71"/>
-      <c r="AD25" s="72"/>
-      <c r="AE25" s="61"/>
-      <c r="AF25" s="62"/>
-      <c r="AG25" s="62"/>
-      <c r="AH25" s="62"/>
-      <c r="AI25" s="63"/>
-    </row>
-    <row r="26" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="43"/>
-      <c r="B26" s="64"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="63"/>
-      <c r="L26" s="61"/>
-      <c r="M26" s="62"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="63"/>
-      <c r="P26" s="70"/>
-      <c r="Q26" s="71"/>
-      <c r="R26" s="71"/>
-      <c r="S26" s="71"/>
-      <c r="T26" s="71"/>
-      <c r="U26" s="71"/>
-      <c r="V26" s="71"/>
-      <c r="W26" s="71"/>
-      <c r="X26" s="71"/>
-      <c r="Y26" s="71"/>
-      <c r="Z26" s="71"/>
-      <c r="AA26" s="71"/>
-      <c r="AB26" s="71"/>
-      <c r="AC26" s="71"/>
-      <c r="AD26" s="72"/>
-      <c r="AE26" s="61"/>
-      <c r="AF26" s="62"/>
-      <c r="AG26" s="62"/>
-      <c r="AH26" s="62"/>
-      <c r="AI26" s="63"/>
-    </row>
-    <row r="27" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="43"/>
-      <c r="B27" s="64"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="61"/>
-      <c r="K27" s="63"/>
-      <c r="L27" s="61"/>
-      <c r="M27" s="62"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="63"/>
-      <c r="P27" s="70"/>
-      <c r="Q27" s="71"/>
-      <c r="R27" s="71"/>
-      <c r="S27" s="71"/>
-      <c r="T27" s="71"/>
-      <c r="U27" s="71"/>
-      <c r="V27" s="71"/>
-      <c r="W27" s="71"/>
-      <c r="X27" s="71"/>
-      <c r="Y27" s="71"/>
-      <c r="Z27" s="71"/>
-      <c r="AA27" s="71"/>
-      <c r="AB27" s="71"/>
-      <c r="AC27" s="71"/>
-      <c r="AD27" s="72"/>
-      <c r="AE27" s="61"/>
-      <c r="AF27" s="62"/>
-      <c r="AG27" s="62"/>
-      <c r="AH27" s="62"/>
-      <c r="AI27" s="63"/>
-    </row>
-    <row r="28" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="43"/>
-      <c r="B28" s="64"/>
-      <c r="C28" s="65"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="61"/>
-      <c r="M28" s="62"/>
-      <c r="N28" s="62"/>
-      <c r="O28" s="63"/>
-      <c r="P28" s="70"/>
-      <c r="Q28" s="71"/>
-      <c r="R28" s="71"/>
-      <c r="S28" s="71"/>
-      <c r="T28" s="71"/>
-      <c r="U28" s="71"/>
-      <c r="V28" s="71"/>
-      <c r="W28" s="71"/>
-      <c r="X28" s="71"/>
-      <c r="Y28" s="71"/>
-      <c r="Z28" s="71"/>
-      <c r="AA28" s="71"/>
-      <c r="AB28" s="71"/>
-      <c r="AC28" s="71"/>
-      <c r="AD28" s="72"/>
-      <c r="AE28" s="61"/>
-      <c r="AF28" s="62"/>
-      <c r="AG28" s="62"/>
-      <c r="AH28" s="62"/>
-      <c r="AI28" s="63"/>
-    </row>
-    <row r="29" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="43"/>
-      <c r="B29" s="64"/>
-      <c r="C29" s="65"/>
-      <c r="D29" s="66"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="69"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="61"/>
-      <c r="K29" s="63"/>
-      <c r="L29" s="61"/>
-      <c r="M29" s="62"/>
-      <c r="N29" s="62"/>
-      <c r="O29" s="63"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="71"/>
-      <c r="R29" s="71"/>
-      <c r="S29" s="71"/>
-      <c r="T29" s="71"/>
-      <c r="U29" s="71"/>
-      <c r="V29" s="71"/>
-      <c r="W29" s="71"/>
-      <c r="X29" s="71"/>
-      <c r="Y29" s="71"/>
-      <c r="Z29" s="71"/>
-      <c r="AA29" s="71"/>
-      <c r="AB29" s="71"/>
-      <c r="AC29" s="71"/>
-      <c r="AD29" s="72"/>
-      <c r="AE29" s="61"/>
-      <c r="AF29" s="62"/>
-      <c r="AG29" s="62"/>
-      <c r="AH29" s="62"/>
-      <c r="AI29" s="63"/>
-    </row>
-    <row r="30" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="43"/>
-      <c r="B30" s="64"/>
-      <c r="C30" s="65"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="63"/>
-      <c r="L30" s="61"/>
-      <c r="M30" s="62"/>
-      <c r="N30" s="62"/>
-      <c r="O30" s="63"/>
-      <c r="P30" s="70"/>
-      <c r="Q30" s="71"/>
-      <c r="R30" s="71"/>
-      <c r="S30" s="71"/>
-      <c r="T30" s="71"/>
-      <c r="U30" s="71"/>
-      <c r="V30" s="71"/>
-      <c r="W30" s="71"/>
-      <c r="X30" s="71"/>
-      <c r="Y30" s="71"/>
-      <c r="Z30" s="71"/>
-      <c r="AA30" s="71"/>
-      <c r="AB30" s="71"/>
-      <c r="AC30" s="71"/>
-      <c r="AD30" s="72"/>
-      <c r="AE30" s="61"/>
-      <c r="AF30" s="62"/>
-      <c r="AG30" s="62"/>
-      <c r="AH30" s="62"/>
-      <c r="AI30" s="63"/>
-    </row>
-    <row r="31" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="43"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="65"/>
-      <c r="D31" s="66"/>
-      <c r="E31" s="67"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="64"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="65"/>
-      <c r="J31" s="61"/>
-      <c r="K31" s="63"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="62"/>
-      <c r="N31" s="62"/>
-      <c r="O31" s="63"/>
-      <c r="P31" s="70"/>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="71"/>
-      <c r="S31" s="71"/>
-      <c r="T31" s="71"/>
-      <c r="U31" s="71"/>
-      <c r="V31" s="71"/>
-      <c r="W31" s="71"/>
-      <c r="X31" s="71"/>
-      <c r="Y31" s="71"/>
-      <c r="Z31" s="71"/>
-      <c r="AA31" s="71"/>
-      <c r="AB31" s="71"/>
-      <c r="AC31" s="71"/>
-      <c r="AD31" s="72"/>
-      <c r="AE31" s="61"/>
-      <c r="AF31" s="62"/>
-      <c r="AG31" s="62"/>
-      <c r="AH31" s="62"/>
-      <c r="AI31" s="63"/>
-    </row>
-    <row r="32" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="43"/>
-      <c r="B32" s="64"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="66"/>
-      <c r="E32" s="67"/>
-      <c r="F32" s="68"/>
-      <c r="G32" s="64"/>
-      <c r="H32" s="69"/>
-      <c r="I32" s="65"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="63"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="62"/>
-      <c r="N32" s="62"/>
-      <c r="O32" s="63"/>
-      <c r="P32" s="70"/>
-      <c r="Q32" s="71"/>
-      <c r="R32" s="71"/>
-      <c r="S32" s="71"/>
-      <c r="T32" s="71"/>
-      <c r="U32" s="71"/>
-      <c r="V32" s="71"/>
-      <c r="W32" s="71"/>
-      <c r="X32" s="71"/>
-      <c r="Y32" s="71"/>
-      <c r="Z32" s="71"/>
-      <c r="AA32" s="71"/>
-      <c r="AB32" s="71"/>
-      <c r="AC32" s="71"/>
-      <c r="AD32" s="72"/>
-      <c r="AE32" s="61"/>
-      <c r="AF32" s="62"/>
-      <c r="AG32" s="62"/>
-      <c r="AH32" s="62"/>
-      <c r="AI32" s="63"/>
-    </row>
-    <row r="33" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="43"/>
-      <c r="B33" s="64"/>
-      <c r="C33" s="65"/>
-      <c r="D33" s="66"/>
-      <c r="E33" s="67"/>
-      <c r="F33" s="68"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="65"/>
-      <c r="J33" s="61"/>
-      <c r="K33" s="63"/>
-      <c r="L33" s="61"/>
-      <c r="M33" s="62"/>
-      <c r="N33" s="62"/>
-      <c r="O33" s="63"/>
-      <c r="P33" s="70"/>
-      <c r="Q33" s="71"/>
-      <c r="R33" s="71"/>
-      <c r="S33" s="71"/>
-      <c r="T33" s="71"/>
-      <c r="U33" s="71"/>
-      <c r="V33" s="71"/>
-      <c r="W33" s="71"/>
-      <c r="X33" s="71"/>
-      <c r="Y33" s="71"/>
-      <c r="Z33" s="71"/>
-      <c r="AA33" s="71"/>
-      <c r="AB33" s="71"/>
-      <c r="AC33" s="71"/>
-      <c r="AD33" s="72"/>
-      <c r="AE33" s="61"/>
-      <c r="AF33" s="62"/>
-      <c r="AG33" s="62"/>
-      <c r="AH33" s="62"/>
-      <c r="AI33" s="63"/>
-    </row>
-    <row r="34" spans="1:35" s="41" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="43"/>
-      <c r="B34" s="64"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="66"/>
-      <c r="E34" s="67"/>
-      <c r="F34" s="68"/>
-      <c r="G34" s="64"/>
-      <c r="H34" s="69"/>
-      <c r="I34" s="65"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="63"/>
-      <c r="L34" s="61"/>
-      <c r="M34" s="62"/>
-      <c r="N34" s="62"/>
-      <c r="O34" s="63"/>
-      <c r="P34" s="70"/>
-      <c r="Q34" s="71"/>
-      <c r="R34" s="71"/>
-      <c r="S34" s="71"/>
-      <c r="T34" s="71"/>
-      <c r="U34" s="71"/>
-      <c r="V34" s="71"/>
-      <c r="W34" s="71"/>
-      <c r="X34" s="71"/>
-      <c r="Y34" s="71"/>
-      <c r="Z34" s="71"/>
-      <c r="AA34" s="71"/>
-      <c r="AB34" s="71"/>
-      <c r="AC34" s="71"/>
-      <c r="AD34" s="72"/>
-      <c r="AE34" s="61"/>
-      <c r="AF34" s="62"/>
-      <c r="AG34" s="62"/>
-      <c r="AH34" s="62"/>
-      <c r="AI34" s="63"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="95"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="88"/>
+      <c r="L9" s="86"/>
+      <c r="M9" s="87"/>
+      <c r="N9" s="87"/>
+      <c r="O9" s="88"/>
+      <c r="P9" s="97" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" s="98"/>
+      <c r="R9" s="98"/>
+      <c r="S9" s="98"/>
+      <c r="T9" s="98"/>
+      <c r="U9" s="98"/>
+      <c r="V9" s="98"/>
+      <c r="W9" s="98"/>
+      <c r="X9" s="98"/>
+      <c r="Y9" s="98"/>
+      <c r="Z9" s="98"/>
+      <c r="AA9" s="98"/>
+      <c r="AB9" s="98"/>
+      <c r="AC9" s="98"/>
+      <c r="AD9" s="99"/>
+      <c r="AE9" s="86" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF9" s="87"/>
+      <c r="AG9" s="87"/>
+      <c r="AH9" s="87"/>
+      <c r="AI9" s="88"/>
+    </row>
+    <row r="10" spans="1:40" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="41"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="58"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="57"/>
+      <c r="N10" s="57"/>
+      <c r="O10" s="58"/>
+      <c r="P10" s="65"/>
+      <c r="Q10" s="66"/>
+      <c r="R10" s="66"/>
+      <c r="S10" s="66"/>
+      <c r="T10" s="66"/>
+      <c r="U10" s="66"/>
+      <c r="V10" s="66"/>
+      <c r="W10" s="66"/>
+      <c r="X10" s="66"/>
+      <c r="Y10" s="66"/>
+      <c r="Z10" s="66"/>
+      <c r="AA10" s="66"/>
+      <c r="AB10" s="66"/>
+      <c r="AC10" s="66"/>
+      <c r="AD10" s="67"/>
+      <c r="AE10" s="56"/>
+      <c r="AF10" s="57"/>
+      <c r="AG10" s="57"/>
+      <c r="AH10" s="57"/>
+      <c r="AI10" s="58"/>
+    </row>
+    <row r="11" spans="1:40" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="41"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="56"/>
+      <c r="K11" s="58"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="57"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="58"/>
+      <c r="P11" s="65"/>
+      <c r="Q11" s="66"/>
+      <c r="R11" s="66"/>
+      <c r="S11" s="66"/>
+      <c r="T11" s="66"/>
+      <c r="U11" s="66"/>
+      <c r="V11" s="66"/>
+      <c r="W11" s="66"/>
+      <c r="X11" s="66"/>
+      <c r="Y11" s="66"/>
+      <c r="Z11" s="66"/>
+      <c r="AA11" s="66"/>
+      <c r="AB11" s="66"/>
+      <c r="AC11" s="66"/>
+      <c r="AD11" s="67"/>
+      <c r="AE11" s="56"/>
+      <c r="AF11" s="57"/>
+      <c r="AG11" s="57"/>
+      <c r="AH11" s="57"/>
+      <c r="AI11" s="58"/>
+    </row>
+    <row r="12" spans="1:40" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="42"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="76"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="79"/>
+      <c r="O12" s="77"/>
+      <c r="P12" s="80"/>
+      <c r="Q12" s="81"/>
+      <c r="R12" s="81"/>
+      <c r="S12" s="81"/>
+      <c r="T12" s="81"/>
+      <c r="U12" s="81"/>
+      <c r="V12" s="81"/>
+      <c r="W12" s="81"/>
+      <c r="X12" s="81"/>
+      <c r="Y12" s="81"/>
+      <c r="Z12" s="81"/>
+      <c r="AA12" s="81"/>
+      <c r="AB12" s="81"/>
+      <c r="AC12" s="81"/>
+      <c r="AD12" s="82"/>
+      <c r="AE12" s="76"/>
+      <c r="AF12" s="79"/>
+      <c r="AG12" s="79"/>
+      <c r="AH12" s="79"/>
+      <c r="AI12" s="77"/>
+    </row>
+    <row r="13" spans="1:40" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="41"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="58"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="57"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="58"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="66"/>
+      <c r="R13" s="66"/>
+      <c r="S13" s="66"/>
+      <c r="T13" s="66"/>
+      <c r="U13" s="66"/>
+      <c r="V13" s="66"/>
+      <c r="W13" s="66"/>
+      <c r="X13" s="66"/>
+      <c r="Y13" s="66"/>
+      <c r="Z13" s="66"/>
+      <c r="AA13" s="66"/>
+      <c r="AB13" s="66"/>
+      <c r="AC13" s="66"/>
+      <c r="AD13" s="67"/>
+      <c r="AE13" s="56"/>
+      <c r="AF13" s="57"/>
+      <c r="AG13" s="57"/>
+      <c r="AH13" s="57"/>
+      <c r="AI13" s="58"/>
+    </row>
+    <row r="14" spans="1:40" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="41"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="58"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="57"/>
+      <c r="N14" s="57"/>
+      <c r="O14" s="58"/>
+      <c r="P14" s="65"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="66"/>
+      <c r="T14" s="66"/>
+      <c r="U14" s="66"/>
+      <c r="V14" s="66"/>
+      <c r="W14" s="66"/>
+      <c r="X14" s="66"/>
+      <c r="Y14" s="66"/>
+      <c r="Z14" s="66"/>
+      <c r="AA14" s="66"/>
+      <c r="AB14" s="66"/>
+      <c r="AC14" s="66"/>
+      <c r="AD14" s="67"/>
+      <c r="AE14" s="56"/>
+      <c r="AF14" s="57"/>
+      <c r="AG14" s="57"/>
+      <c r="AH14" s="57"/>
+      <c r="AI14" s="58"/>
+    </row>
+    <row r="15" spans="1:40" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="41"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="58"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="57"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="58"/>
+      <c r="P15" s="65"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
+      <c r="S15" s="66"/>
+      <c r="T15" s="66"/>
+      <c r="U15" s="66"/>
+      <c r="V15" s="66"/>
+      <c r="W15" s="66"/>
+      <c r="X15" s="66"/>
+      <c r="Y15" s="66"/>
+      <c r="Z15" s="66"/>
+      <c r="AA15" s="66"/>
+      <c r="AB15" s="66"/>
+      <c r="AC15" s="66"/>
+      <c r="AD15" s="67"/>
+      <c r="AE15" s="56"/>
+      <c r="AF15" s="57"/>
+      <c r="AG15" s="57"/>
+      <c r="AH15" s="57"/>
+      <c r="AI15" s="58"/>
+    </row>
+    <row r="16" spans="1:40" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="41"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="57"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="65"/>
+      <c r="Q16" s="66"/>
+      <c r="R16" s="66"/>
+      <c r="S16" s="66"/>
+      <c r="T16" s="66"/>
+      <c r="U16" s="66"/>
+      <c r="V16" s="66"/>
+      <c r="W16" s="66"/>
+      <c r="X16" s="66"/>
+      <c r="Y16" s="66"/>
+      <c r="Z16" s="66"/>
+      <c r="AA16" s="66"/>
+      <c r="AB16" s="66"/>
+      <c r="AC16" s="66"/>
+      <c r="AD16" s="67"/>
+      <c r="AE16" s="56"/>
+      <c r="AF16" s="57"/>
+      <c r="AG16" s="57"/>
+      <c r="AH16" s="57"/>
+      <c r="AI16" s="58"/>
+    </row>
+    <row r="17" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="41"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="56"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="57"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="65"/>
+      <c r="Q17" s="66"/>
+      <c r="R17" s="66"/>
+      <c r="S17" s="66"/>
+      <c r="T17" s="66"/>
+      <c r="U17" s="66"/>
+      <c r="V17" s="66"/>
+      <c r="W17" s="66"/>
+      <c r="X17" s="66"/>
+      <c r="Y17" s="66"/>
+      <c r="Z17" s="66"/>
+      <c r="AA17" s="66"/>
+      <c r="AB17" s="66"/>
+      <c r="AC17" s="66"/>
+      <c r="AD17" s="67"/>
+      <c r="AE17" s="56"/>
+      <c r="AF17" s="57"/>
+      <c r="AG17" s="57"/>
+      <c r="AH17" s="57"/>
+      <c r="AI17" s="58"/>
+    </row>
+    <row r="18" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="41"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="58"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="57"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="58"/>
+      <c r="P18" s="65"/>
+      <c r="Q18" s="66"/>
+      <c r="R18" s="66"/>
+      <c r="S18" s="66"/>
+      <c r="T18" s="66"/>
+      <c r="U18" s="66"/>
+      <c r="V18" s="66"/>
+      <c r="W18" s="66"/>
+      <c r="X18" s="66"/>
+      <c r="Y18" s="66"/>
+      <c r="Z18" s="66"/>
+      <c r="AA18" s="66"/>
+      <c r="AB18" s="66"/>
+      <c r="AC18" s="66"/>
+      <c r="AD18" s="67"/>
+      <c r="AE18" s="56"/>
+      <c r="AF18" s="57"/>
+      <c r="AG18" s="57"/>
+      <c r="AH18" s="57"/>
+      <c r="AI18" s="58"/>
+    </row>
+    <row r="19" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="41"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="65"/>
+      <c r="Q19" s="66"/>
+      <c r="R19" s="66"/>
+      <c r="S19" s="66"/>
+      <c r="T19" s="66"/>
+      <c r="U19" s="66"/>
+      <c r="V19" s="66"/>
+      <c r="W19" s="66"/>
+      <c r="X19" s="66"/>
+      <c r="Y19" s="66"/>
+      <c r="Z19" s="66"/>
+      <c r="AA19" s="66"/>
+      <c r="AB19" s="66"/>
+      <c r="AC19" s="66"/>
+      <c r="AD19" s="67"/>
+      <c r="AE19" s="56"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="58"/>
+    </row>
+    <row r="20" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="41"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="58"/>
+      <c r="P20" s="65"/>
+      <c r="Q20" s="66"/>
+      <c r="R20" s="66"/>
+      <c r="S20" s="66"/>
+      <c r="T20" s="66"/>
+      <c r="U20" s="66"/>
+      <c r="V20" s="66"/>
+      <c r="W20" s="66"/>
+      <c r="X20" s="66"/>
+      <c r="Y20" s="66"/>
+      <c r="Z20" s="66"/>
+      <c r="AA20" s="66"/>
+      <c r="AB20" s="66"/>
+      <c r="AC20" s="66"/>
+      <c r="AD20" s="67"/>
+      <c r="AE20" s="56"/>
+      <c r="AF20" s="57"/>
+      <c r="AG20" s="57"/>
+      <c r="AH20" s="57"/>
+      <c r="AI20" s="58"/>
+    </row>
+    <row r="21" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="41"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="58"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="58"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="66"/>
+      <c r="R21" s="66"/>
+      <c r="S21" s="66"/>
+      <c r="T21" s="66"/>
+      <c r="U21" s="66"/>
+      <c r="V21" s="66"/>
+      <c r="W21" s="66"/>
+      <c r="X21" s="66"/>
+      <c r="Y21" s="66"/>
+      <c r="Z21" s="66"/>
+      <c r="AA21" s="66"/>
+      <c r="AB21" s="66"/>
+      <c r="AC21" s="66"/>
+      <c r="AD21" s="67"/>
+      <c r="AE21" s="56"/>
+      <c r="AF21" s="57"/>
+      <c r="AG21" s="57"/>
+      <c r="AH21" s="57"/>
+      <c r="AI21" s="58"/>
+    </row>
+    <row r="22" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="41"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="58"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="57"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="58"/>
+      <c r="P22" s="65"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="66"/>
+      <c r="V22" s="66"/>
+      <c r="W22" s="66"/>
+      <c r="X22" s="66"/>
+      <c r="Y22" s="66"/>
+      <c r="Z22" s="66"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="66"/>
+      <c r="AC22" s="66"/>
+      <c r="AD22" s="67"/>
+      <c r="AE22" s="56"/>
+      <c r="AF22" s="57"/>
+      <c r="AG22" s="57"/>
+      <c r="AH22" s="57"/>
+      <c r="AI22" s="58"/>
+    </row>
+    <row r="23" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="41"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="58"/>
+      <c r="P23" s="65"/>
+      <c r="Q23" s="66"/>
+      <c r="R23" s="66"/>
+      <c r="S23" s="66"/>
+      <c r="T23" s="66"/>
+      <c r="U23" s="66"/>
+      <c r="V23" s="66"/>
+      <c r="W23" s="66"/>
+      <c r="X23" s="66"/>
+      <c r="Y23" s="66"/>
+      <c r="Z23" s="66"/>
+      <c r="AA23" s="66"/>
+      <c r="AB23" s="66"/>
+      <c r="AC23" s="66"/>
+      <c r="AD23" s="67"/>
+      <c r="AE23" s="56"/>
+      <c r="AF23" s="57"/>
+      <c r="AG23" s="57"/>
+      <c r="AH23" s="57"/>
+      <c r="AI23" s="58"/>
+    </row>
+    <row r="24" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="41"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="57"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="58"/>
+      <c r="P24" s="65"/>
+      <c r="Q24" s="66"/>
+      <c r="R24" s="66"/>
+      <c r="S24" s="66"/>
+      <c r="T24" s="66"/>
+      <c r="U24" s="66"/>
+      <c r="V24" s="66"/>
+      <c r="W24" s="66"/>
+      <c r="X24" s="66"/>
+      <c r="Y24" s="66"/>
+      <c r="Z24" s="66"/>
+      <c r="AA24" s="66"/>
+      <c r="AB24" s="66"/>
+      <c r="AC24" s="66"/>
+      <c r="AD24" s="67"/>
+      <c r="AE24" s="56"/>
+      <c r="AF24" s="57"/>
+      <c r="AG24" s="57"/>
+      <c r="AH24" s="57"/>
+      <c r="AI24" s="58"/>
+    </row>
+    <row r="25" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="41"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="60"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="58"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="58"/>
+      <c r="P25" s="65"/>
+      <c r="Q25" s="66"/>
+      <c r="R25" s="66"/>
+      <c r="S25" s="66"/>
+      <c r="T25" s="66"/>
+      <c r="U25" s="66"/>
+      <c r="V25" s="66"/>
+      <c r="W25" s="66"/>
+      <c r="X25" s="66"/>
+      <c r="Y25" s="66"/>
+      <c r="Z25" s="66"/>
+      <c r="AA25" s="66"/>
+      <c r="AB25" s="66"/>
+      <c r="AC25" s="66"/>
+      <c r="AD25" s="67"/>
+      <c r="AE25" s="56"/>
+      <c r="AF25" s="57"/>
+      <c r="AG25" s="57"/>
+      <c r="AH25" s="57"/>
+      <c r="AI25" s="58"/>
+    </row>
+    <row r="26" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="41"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="56"/>
+      <c r="K26" s="58"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="58"/>
+      <c r="P26" s="65"/>
+      <c r="Q26" s="66"/>
+      <c r="R26" s="66"/>
+      <c r="S26" s="66"/>
+      <c r="T26" s="66"/>
+      <c r="U26" s="66"/>
+      <c r="V26" s="66"/>
+      <c r="W26" s="66"/>
+      <c r="X26" s="66"/>
+      <c r="Y26" s="66"/>
+      <c r="Z26" s="66"/>
+      <c r="AA26" s="66"/>
+      <c r="AB26" s="66"/>
+      <c r="AC26" s="66"/>
+      <c r="AD26" s="67"/>
+      <c r="AE26" s="56"/>
+      <c r="AF26" s="57"/>
+      <c r="AG26" s="57"/>
+      <c r="AH26" s="57"/>
+      <c r="AI26" s="58"/>
+    </row>
+    <row r="27" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="41"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="57"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="58"/>
+      <c r="P27" s="65"/>
+      <c r="Q27" s="66"/>
+      <c r="R27" s="66"/>
+      <c r="S27" s="66"/>
+      <c r="T27" s="66"/>
+      <c r="U27" s="66"/>
+      <c r="V27" s="66"/>
+      <c r="W27" s="66"/>
+      <c r="X27" s="66"/>
+      <c r="Y27" s="66"/>
+      <c r="Z27" s="66"/>
+      <c r="AA27" s="66"/>
+      <c r="AB27" s="66"/>
+      <c r="AC27" s="66"/>
+      <c r="AD27" s="67"/>
+      <c r="AE27" s="56"/>
+      <c r="AF27" s="57"/>
+      <c r="AG27" s="57"/>
+      <c r="AH27" s="57"/>
+      <c r="AI27" s="58"/>
+    </row>
+    <row r="28" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="41"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="65"/>
+      <c r="Q28" s="66"/>
+      <c r="R28" s="66"/>
+      <c r="S28" s="66"/>
+      <c r="T28" s="66"/>
+      <c r="U28" s="66"/>
+      <c r="V28" s="66"/>
+      <c r="W28" s="66"/>
+      <c r="X28" s="66"/>
+      <c r="Y28" s="66"/>
+      <c r="Z28" s="66"/>
+      <c r="AA28" s="66"/>
+      <c r="AB28" s="66"/>
+      <c r="AC28" s="66"/>
+      <c r="AD28" s="67"/>
+      <c r="AE28" s="56"/>
+      <c r="AF28" s="57"/>
+      <c r="AG28" s="57"/>
+      <c r="AH28" s="57"/>
+      <c r="AI28" s="58"/>
+    </row>
+    <row r="29" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="41"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="56"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="58"/>
+      <c r="P29" s="65"/>
+      <c r="Q29" s="66"/>
+      <c r="R29" s="66"/>
+      <c r="S29" s="66"/>
+      <c r="T29" s="66"/>
+      <c r="U29" s="66"/>
+      <c r="V29" s="66"/>
+      <c r="W29" s="66"/>
+      <c r="X29" s="66"/>
+      <c r="Y29" s="66"/>
+      <c r="Z29" s="66"/>
+      <c r="AA29" s="66"/>
+      <c r="AB29" s="66"/>
+      <c r="AC29" s="66"/>
+      <c r="AD29" s="67"/>
+      <c r="AE29" s="56"/>
+      <c r="AF29" s="57"/>
+      <c r="AG29" s="57"/>
+      <c r="AH29" s="57"/>
+      <c r="AI29" s="58"/>
+    </row>
+    <row r="30" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="41"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="58"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="58"/>
+      <c r="P30" s="65"/>
+      <c r="Q30" s="66"/>
+      <c r="R30" s="66"/>
+      <c r="S30" s="66"/>
+      <c r="T30" s="66"/>
+      <c r="U30" s="66"/>
+      <c r="V30" s="66"/>
+      <c r="W30" s="66"/>
+      <c r="X30" s="66"/>
+      <c r="Y30" s="66"/>
+      <c r="Z30" s="66"/>
+      <c r="AA30" s="66"/>
+      <c r="AB30" s="66"/>
+      <c r="AC30" s="66"/>
+      <c r="AD30" s="67"/>
+      <c r="AE30" s="56"/>
+      <c r="AF30" s="57"/>
+      <c r="AG30" s="57"/>
+      <c r="AH30" s="57"/>
+      <c r="AI30" s="58"/>
+    </row>
+    <row r="31" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="41"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="56"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="57"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="65"/>
+      <c r="Q31" s="66"/>
+      <c r="R31" s="66"/>
+      <c r="S31" s="66"/>
+      <c r="T31" s="66"/>
+      <c r="U31" s="66"/>
+      <c r="V31" s="66"/>
+      <c r="W31" s="66"/>
+      <c r="X31" s="66"/>
+      <c r="Y31" s="66"/>
+      <c r="Z31" s="66"/>
+      <c r="AA31" s="66"/>
+      <c r="AB31" s="66"/>
+      <c r="AC31" s="66"/>
+      <c r="AD31" s="67"/>
+      <c r="AE31" s="56"/>
+      <c r="AF31" s="57"/>
+      <c r="AG31" s="57"/>
+      <c r="AH31" s="57"/>
+      <c r="AI31" s="58"/>
+    </row>
+    <row r="32" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="41"/>
+      <c r="B32" s="59"/>
+      <c r="C32" s="60"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="58"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="57"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="65"/>
+      <c r="Q32" s="66"/>
+      <c r="R32" s="66"/>
+      <c r="S32" s="66"/>
+      <c r="T32" s="66"/>
+      <c r="U32" s="66"/>
+      <c r="V32" s="66"/>
+      <c r="W32" s="66"/>
+      <c r="X32" s="66"/>
+      <c r="Y32" s="66"/>
+      <c r="Z32" s="66"/>
+      <c r="AA32" s="66"/>
+      <c r="AB32" s="66"/>
+      <c r="AC32" s="66"/>
+      <c r="AD32" s="67"/>
+      <c r="AE32" s="56"/>
+      <c r="AF32" s="57"/>
+      <c r="AG32" s="57"/>
+      <c r="AH32" s="57"/>
+      <c r="AI32" s="58"/>
+    </row>
+    <row r="33" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="41"/>
+      <c r="B33" s="59"/>
+      <c r="C33" s="60"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="60"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="58"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="57"/>
+      <c r="O33" s="58"/>
+      <c r="P33" s="65"/>
+      <c r="Q33" s="66"/>
+      <c r="R33" s="66"/>
+      <c r="S33" s="66"/>
+      <c r="T33" s="66"/>
+      <c r="U33" s="66"/>
+      <c r="V33" s="66"/>
+      <c r="W33" s="66"/>
+      <c r="X33" s="66"/>
+      <c r="Y33" s="66"/>
+      <c r="Z33" s="66"/>
+      <c r="AA33" s="66"/>
+      <c r="AB33" s="66"/>
+      <c r="AC33" s="66"/>
+      <c r="AD33" s="67"/>
+      <c r="AE33" s="56"/>
+      <c r="AF33" s="57"/>
+      <c r="AG33" s="57"/>
+      <c r="AH33" s="57"/>
+      <c r="AI33" s="58"/>
+    </row>
+    <row r="34" spans="1:35" s="39" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="41"/>
+      <c r="B34" s="59"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="63"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="58"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="57"/>
+      <c r="O34" s="58"/>
+      <c r="P34" s="65"/>
+      <c r="Q34" s="66"/>
+      <c r="R34" s="66"/>
+      <c r="S34" s="66"/>
+      <c r="T34" s="66"/>
+      <c r="U34" s="66"/>
+      <c r="V34" s="66"/>
+      <c r="W34" s="66"/>
+      <c r="X34" s="66"/>
+      <c r="Y34" s="66"/>
+      <c r="Z34" s="66"/>
+      <c r="AA34" s="66"/>
+      <c r="AB34" s="66"/>
+      <c r="AC34" s="66"/>
+      <c r="AD34" s="67"/>
+      <c r="AE34" s="56"/>
+      <c r="AF34" s="57"/>
+      <c r="AG34" s="57"/>
+      <c r="AH34" s="57"/>
+      <c r="AI34" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="202">
@@ -8810,1650 +8864,1662 @@
   <phoneticPr fontId="4"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" firstPageNumber="4" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <headerFooter scaleWithDoc="0" alignWithMargins="0">
-    <oddFooter>&amp;LCopyright(c) 2016 TIS Inc.</oddFooter>
-  </headerFooter>
+  <headerFooter scaleWithDoc="0" alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AL132"/>
+  <dimension ref="A1:AL151"/>
   <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.83203125" style="45"/>
-    <col min="2" max="2" width="4.83203125" style="45" customWidth="1"/>
-    <col min="3" max="16" width="4.83203125" style="45"/>
-    <col min="17" max="17" width="4.83203125" style="45" customWidth="1"/>
-    <col min="18" max="16384" width="4.83203125" style="45"/>
+    <col min="1" max="1" width="4.83203125" style="43"/>
+    <col min="2" max="2" width="4.83203125" style="43" customWidth="1"/>
+    <col min="3" max="16" width="4.83203125" style="43"/>
+    <col min="17" max="17" width="4.83203125" style="43" customWidth="1"/>
+    <col min="18" max="16384" width="4.83203125" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="25" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="122" t="str">
+    <row r="1" spans="1:38" s="24" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="114" t="str">
         <f>IF(変更履歴!E1&lt;&gt;"",変更履歴!E1,"")</f>
         <v>XXXプロジェクト</v>
       </c>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="123"/>
-      <c r="K1" s="123"/>
-      <c r="L1" s="123"/>
-      <c r="M1" s="123"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="125" t="str">
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="117" t="str">
         <f>IF(変更履歴!Q1&lt;&gt;"",変更履歴!Q1,"")</f>
         <v>要件定義</v>
       </c>
-      <c r="R1" s="126"/>
-      <c r="S1" s="126"/>
-      <c r="T1" s="126"/>
-      <c r="U1" s="126"/>
-      <c r="V1" s="126"/>
-      <c r="W1" s="126"/>
-      <c r="X1" s="127"/>
-      <c r="Y1" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="128" t="str">
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
+      <c r="V1" s="118"/>
+      <c r="W1" s="118"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z1" s="21"/>
+      <c r="AA1" s="120" t="str">
         <f>IF(変更履歴!AA1&lt;&gt;"",変更履歴!AA1,"")</f>
         <v/>
       </c>
-      <c r="AB1" s="129"/>
-      <c r="AC1" s="129"/>
-      <c r="AD1" s="129"/>
-      <c r="AE1" s="130"/>
-      <c r="AF1" s="140" t="str">
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="121"/>
+      <c r="AE1" s="122"/>
+      <c r="AF1" s="132" t="str">
         <f>IF(変更履歴!AF1&lt;&gt;"",変更履歴!AF1,"")</f>
         <v/>
       </c>
-      <c r="AG1" s="141"/>
-      <c r="AH1" s="141"/>
-      <c r="AI1" s="142"/>
-      <c r="AJ1" s="23"/>
-      <c r="AK1" s="23"/>
-      <c r="AL1" s="24"/>
-    </row>
-    <row r="2" spans="1:38" s="25" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="122" t="str">
+      <c r="AG1" s="133"/>
+      <c r="AH1" s="133"/>
+      <c r="AI1" s="134"/>
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="22"/>
+      <c r="AL1" s="23"/>
+    </row>
+    <row r="2" spans="1:38" s="24" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="114" t="str">
         <f>IF(変更履歴!E2&lt;&gt;"",変更履歴!E2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="123"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="123"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="149" t="str">
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="115"/>
+      <c r="M2" s="115"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="141" t="str">
         <f>IF(変更履歴!Q2&lt;&gt;"",変更履歴!Q2,"")</f>
         <v>アプリケーション方式設計書</v>
       </c>
-      <c r="R2" s="150"/>
-      <c r="S2" s="150"/>
-      <c r="T2" s="150"/>
-      <c r="U2" s="150"/>
-      <c r="V2" s="150"/>
-      <c r="W2" s="150"/>
-      <c r="X2" s="151"/>
-      <c r="Y2" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z2" s="22"/>
-      <c r="AA2" s="128" t="str">
+      <c r="R2" s="142"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="142"/>
+      <c r="U2" s="142"/>
+      <c r="V2" s="142"/>
+      <c r="W2" s="142"/>
+      <c r="X2" s="143"/>
+      <c r="Y2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z2" s="21"/>
+      <c r="AA2" s="120" t="str">
         <f>IF(変更履歴!AA2&lt;&gt;"",変更履歴!AA2,"")</f>
         <v/>
       </c>
-      <c r="AB2" s="129"/>
-      <c r="AC2" s="129"/>
-      <c r="AD2" s="129"/>
-      <c r="AE2" s="130"/>
-      <c r="AF2" s="140" t="str">
+      <c r="AB2" s="121"/>
+      <c r="AC2" s="121"/>
+      <c r="AD2" s="121"/>
+      <c r="AE2" s="122"/>
+      <c r="AF2" s="132" t="str">
         <f>IF(変更履歴!AF2&lt;&gt;"",変更履歴!AF2,"")</f>
         <v/>
       </c>
-      <c r="AG2" s="141"/>
-      <c r="AH2" s="141"/>
-      <c r="AI2" s="142"/>
-      <c r="AJ2" s="23"/>
-      <c r="AK2" s="23"/>
-      <c r="AL2" s="23"/>
-    </row>
-    <row r="3" spans="1:38" s="25" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="122" t="str">
+      <c r="AG2" s="133"/>
+      <c r="AH2" s="133"/>
+      <c r="AI2" s="134"/>
+      <c r="AJ2" s="22"/>
+      <c r="AK2" s="22"/>
+      <c r="AL2" s="22"/>
+    </row>
+    <row r="3" spans="1:38" s="24" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="29"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="114" t="str">
         <f>IF(変更履歴!E3&lt;&gt;"",変更履歴!E3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
-      <c r="J3" s="123"/>
-      <c r="K3" s="123"/>
-      <c r="L3" s="123"/>
-      <c r="M3" s="123"/>
-      <c r="N3" s="124"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="152"/>
-      <c r="R3" s="153"/>
-      <c r="S3" s="153"/>
-      <c r="T3" s="153"/>
-      <c r="U3" s="153"/>
-      <c r="V3" s="153"/>
-      <c r="W3" s="153"/>
-      <c r="X3" s="154"/>
-      <c r="Y3" s="33"/>
-      <c r="Z3" s="35"/>
-      <c r="AA3" s="128"/>
-      <c r="AB3" s="129"/>
-      <c r="AC3" s="129"/>
-      <c r="AD3" s="129"/>
-      <c r="AE3" s="130"/>
-      <c r="AF3" s="146"/>
-      <c r="AG3" s="147"/>
-      <c r="AH3" s="147"/>
-      <c r="AI3" s="148"/>
-      <c r="AJ3" s="23"/>
-      <c r="AK3" s="23"/>
-      <c r="AL3" s="23"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="116"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="144"/>
+      <c r="R3" s="145"/>
+      <c r="S3" s="145"/>
+      <c r="T3" s="145"/>
+      <c r="U3" s="145"/>
+      <c r="V3" s="145"/>
+      <c r="W3" s="145"/>
+      <c r="X3" s="146"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="34"/>
+      <c r="AA3" s="120"/>
+      <c r="AB3" s="121"/>
+      <c r="AC3" s="121"/>
+      <c r="AD3" s="121"/>
+      <c r="AE3" s="122"/>
+      <c r="AF3" s="138"/>
+      <c r="AG3" s="139"/>
+      <c r="AH3" s="139"/>
+      <c r="AI3" s="140"/>
+      <c r="AJ3" s="22"/>
+      <c r="AK3" s="22"/>
+      <c r="AL3" s="22"/>
     </row>
     <row r="4" spans="1:38" ht="12" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:38" s="46" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q5" s="47" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:38" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:38" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="48"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-    </row>
-    <row r="8" spans="1:38" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="48"/>
-      <c r="C8" s="46" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:38" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="48"/>
-      <c r="B9" s="50"/>
-    </row>
-    <row r="10" spans="1:38" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="48"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="O10" s="49"/>
-      <c r="P10" s="49"/>
-    </row>
-    <row r="11" spans="1:38" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="48"/>
-      <c r="B11" s="51"/>
-      <c r="D11" s="46" t="s">
+    <row r="5" spans="1:38" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q5" s="45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="7" spans="1:38" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="46"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="47"/>
+    </row>
+    <row r="8" spans="1:38" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="46"/>
+      <c r="C8" s="44" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="46"/>
+      <c r="D9" s="44" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="46"/>
+      <c r="D10" s="44" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="46"/>
+      <c r="D11" s="44" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="46"/>
+      <c r="D12" s="44" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="46"/>
+      <c r="B13" s="48"/>
+    </row>
+    <row r="14" spans="1:38" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="46"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="O14" s="47"/>
+      <c r="P14" s="47"/>
+    </row>
+    <row r="15" spans="1:38" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="46"/>
+      <c r="B15" s="48"/>
+      <c r="D15" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="O15" s="47"/>
+      <c r="P15" s="47"/>
+    </row>
+    <row r="16" spans="1:38" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="46"/>
+      <c r="B16" s="48"/>
+      <c r="D16" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="O16" s="47"/>
+      <c r="P16" s="47"/>
+    </row>
+    <row r="17" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="46"/>
+      <c r="B17" s="48"/>
+      <c r="D17" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="O17" s="47"/>
+      <c r="P17" s="47"/>
+    </row>
+    <row r="18" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="46"/>
+      <c r="B18" s="48"/>
+      <c r="D18" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="O18" s="47"/>
+      <c r="P18" s="47"/>
+    </row>
+    <row r="19" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="46"/>
+      <c r="B19" s="48"/>
+      <c r="E19" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="O19" s="47"/>
+      <c r="P19" s="47"/>
+    </row>
+    <row r="20" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="46"/>
+    </row>
+    <row r="21" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="46"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="44" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="46"/>
+      <c r="B22" s="49"/>
+      <c r="D22" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="O22" s="47"/>
+      <c r="P22" s="47"/>
+    </row>
+    <row r="23" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="46"/>
+      <c r="B23" s="49"/>
+      <c r="E23" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="O23" s="47"/>
+      <c r="P23" s="47"/>
+    </row>
+    <row r="24" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="46"/>
+      <c r="B24" s="49"/>
+      <c r="E24" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="O24" s="47"/>
+      <c r="P24" s="47"/>
+    </row>
+    <row r="25" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="46"/>
+      <c r="B25" s="49"/>
+      <c r="E25" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="O25" s="47"/>
+      <c r="P25" s="47"/>
+    </row>
+    <row r="26" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="46"/>
+      <c r="B26" s="49"/>
+      <c r="E26" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="O26" s="47"/>
+      <c r="P26" s="47"/>
+    </row>
+    <row r="27" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="46"/>
+      <c r="B27" s="49"/>
+      <c r="E27" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="O27" s="47"/>
+      <c r="P27" s="47"/>
+    </row>
+    <row r="28" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="46"/>
+      <c r="B28" s="49"/>
+      <c r="E28" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="O28" s="47"/>
+      <c r="P28" s="47"/>
+    </row>
+    <row r="29" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="46"/>
+      <c r="B29" s="49"/>
+      <c r="E29" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="O29" s="47"/>
+      <c r="P29" s="47"/>
+    </row>
+    <row r="30" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="46"/>
+      <c r="B30" s="49"/>
+      <c r="E30" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="O30" s="47"/>
+      <c r="P30" s="47"/>
+    </row>
+    <row r="31" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="46"/>
+      <c r="B31" s="49"/>
+      <c r="E31" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="O31" s="47"/>
+      <c r="P31" s="47"/>
+    </row>
+    <row r="32" spans="1:16" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="46"/>
+      <c r="B32" s="49"/>
+      <c r="E32" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="O32" s="47"/>
+      <c r="P32" s="47"/>
+    </row>
+    <row r="33" spans="1:24" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="46"/>
+      <c r="B33" s="49"/>
+      <c r="E33" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="O33" s="47"/>
+      <c r="P33" s="47"/>
+    </row>
+    <row r="34" spans="1:24" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="46"/>
+      <c r="B34" s="49"/>
+      <c r="E34" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="O34" s="47"/>
+      <c r="P34" s="47"/>
+    </row>
+    <row r="35" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="46"/>
+      <c r="D35" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="O35" s="47"/>
+    </row>
+    <row r="36" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="46"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="O36" s="47"/>
+    </row>
+    <row r="37" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="46"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="O37" s="47"/>
+    </row>
+    <row r="38" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="46"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="O11" s="49"/>
-      <c r="P11" s="49"/>
-    </row>
-    <row r="12" spans="1:38" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="48"/>
-      <c r="B12" s="51"/>
-      <c r="D12" s="46" t="s">
+      <c r="O38" s="47"/>
+    </row>
+    <row r="39" spans="1:24" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="46"/>
+      <c r="O39" s="47"/>
+      <c r="P39" s="47"/>
+    </row>
+    <row r="40" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="50"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="O12" s="49"/>
-      <c r="P12" s="49"/>
-    </row>
-    <row r="13" spans="1:38" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="48"/>
-      <c r="B13" s="51"/>
-      <c r="D13" s="46" t="s">
+      <c r="D40" s="43"/>
+      <c r="O40" s="47"/>
+      <c r="P40" s="47"/>
+      <c r="R40" s="43"/>
+      <c r="S40" s="43"/>
+      <c r="T40" s="43"/>
+      <c r="U40" s="43"/>
+      <c r="V40" s="43"/>
+      <c r="W40" s="43"/>
+      <c r="X40" s="43"/>
+    </row>
+    <row r="41" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="50"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="O13" s="49"/>
-      <c r="P13" s="49"/>
-    </row>
-    <row r="14" spans="1:38" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="48"/>
-      <c r="B14" s="51"/>
-      <c r="D14" s="46" t="s">
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+      <c r="L41" s="43"/>
+      <c r="M41" s="43"/>
+      <c r="N41" s="47"/>
+      <c r="O41" s="47"/>
+      <c r="P41" s="43"/>
+      <c r="R41" s="43"/>
+      <c r="S41" s="43"/>
+      <c r="T41" s="43"/>
+      <c r="U41" s="43"/>
+      <c r="V41" s="43"/>
+      <c r="W41" s="43"/>
+      <c r="X41" s="43"/>
+    </row>
+    <row r="42" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="50"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="O14" s="49"/>
-      <c r="P14" s="49"/>
-    </row>
-    <row r="15" spans="1:38" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="48"/>
-    </row>
-    <row r="16" spans="1:38" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="48"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="46" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="48"/>
-      <c r="B17" s="52"/>
-      <c r="D17" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="O17" s="49"/>
-      <c r="P17" s="49"/>
-    </row>
-    <row r="18" spans="1:16" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="48"/>
-      <c r="B18" s="52"/>
-      <c r="E18" s="46" t="s">
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+      <c r="L42" s="43"/>
+      <c r="M42" s="43"/>
+      <c r="N42" s="47"/>
+      <c r="O42" s="47"/>
+      <c r="P42" s="43"/>
+      <c r="R42" s="43"/>
+      <c r="S42" s="43"/>
+      <c r="T42" s="43"/>
+      <c r="U42" s="43"/>
+      <c r="V42" s="43"/>
+      <c r="W42" s="43"/>
+      <c r="X42" s="43"/>
+    </row>
+    <row r="43" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="50"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="O18" s="49"/>
-      <c r="P18" s="49"/>
-    </row>
-    <row r="19" spans="1:16" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="48"/>
-      <c r="B19" s="52"/>
-      <c r="E19" s="46" t="s">
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+      <c r="L43" s="43"/>
+      <c r="M43" s="43"/>
+      <c r="N43" s="47"/>
+      <c r="O43" s="47"/>
+      <c r="P43" s="43"/>
+      <c r="R43" s="43"/>
+      <c r="S43" s="43"/>
+      <c r="T43" s="43"/>
+      <c r="U43" s="43"/>
+      <c r="V43" s="43"/>
+      <c r="W43" s="43"/>
+      <c r="X43" s="43"/>
+    </row>
+    <row r="44" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="50"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="O19" s="49"/>
-      <c r="P19" s="49"/>
-    </row>
-    <row r="20" spans="1:16" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="48"/>
-      <c r="B20" s="52"/>
-      <c r="E20" s="46" t="s">
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+      <c r="L44" s="43"/>
+      <c r="M44" s="43"/>
+      <c r="N44" s="47"/>
+      <c r="O44" s="47"/>
+      <c r="P44" s="43"/>
+      <c r="R44" s="43"/>
+      <c r="S44" s="43"/>
+      <c r="T44" s="43"/>
+      <c r="U44" s="43"/>
+      <c r="V44" s="43"/>
+      <c r="W44" s="43"/>
+      <c r="X44" s="43"/>
+    </row>
+    <row r="45" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="50"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="O20" s="49"/>
-      <c r="P20" s="49"/>
-    </row>
-    <row r="21" spans="1:16" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="48"/>
-      <c r="B21" s="52"/>
-      <c r="E21" s="46" t="s">
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+      <c r="L45" s="43"/>
+      <c r="M45" s="43"/>
+      <c r="N45" s="47"/>
+      <c r="O45" s="47"/>
+      <c r="P45" s="43"/>
+      <c r="R45" s="43"/>
+      <c r="S45" s="43"/>
+      <c r="T45" s="43"/>
+      <c r="U45" s="43"/>
+      <c r="V45" s="43"/>
+      <c r="W45" s="43"/>
+      <c r="X45" s="43"/>
+    </row>
+    <row r="46" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="50"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="O21" s="49"/>
-      <c r="P21" s="49"/>
-    </row>
-    <row r="22" spans="1:16" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="48"/>
-      <c r="B22" s="52"/>
-      <c r="E22" s="46" t="s">
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="43"/>
+      <c r="M46" s="43"/>
+      <c r="N46" s="47"/>
+      <c r="O46" s="47"/>
+      <c r="P46" s="43"/>
+      <c r="R46" s="43"/>
+      <c r="S46" s="43"/>
+      <c r="T46" s="43"/>
+      <c r="U46" s="43"/>
+      <c r="V46" s="43"/>
+      <c r="W46" s="43"/>
+      <c r="X46" s="43"/>
+    </row>
+    <row r="47" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="50"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+      <c r="L47" s="43"/>
+      <c r="M47" s="43"/>
+      <c r="N47" s="47"/>
+      <c r="O47" s="47"/>
+      <c r="P47" s="43"/>
+      <c r="R47" s="43"/>
+      <c r="S47" s="43"/>
+      <c r="T47" s="43"/>
+      <c r="U47" s="43"/>
+      <c r="V47" s="43"/>
+      <c r="W47" s="43"/>
+      <c r="X47" s="43"/>
+    </row>
+    <row r="48" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="50"/>
+      <c r="B48" s="49"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+      <c r="L48" s="43"/>
+      <c r="M48" s="43"/>
+      <c r="N48" s="47"/>
+      <c r="O48" s="47"/>
+      <c r="P48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="43"/>
+      <c r="T48" s="43"/>
+      <c r="U48" s="43"/>
+      <c r="V48" s="43"/>
+      <c r="W48" s="43"/>
+      <c r="X48" s="43"/>
+    </row>
+    <row r="49" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="50"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="43"/>
+      <c r="L49" s="43"/>
+      <c r="M49" s="43"/>
+      <c r="N49" s="47"/>
+      <c r="O49" s="47"/>
+      <c r="P49" s="43"/>
+      <c r="R49" s="43"/>
+      <c r="S49" s="43"/>
+      <c r="T49" s="43"/>
+      <c r="U49" s="43"/>
+      <c r="V49" s="43"/>
+      <c r="W49" s="43"/>
+      <c r="X49" s="43"/>
+    </row>
+    <row r="50" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="50"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+      <c r="L50" s="43"/>
+      <c r="M50" s="43"/>
+      <c r="N50" s="47"/>
+      <c r="O50" s="47"/>
+      <c r="P50" s="43"/>
+      <c r="R50" s="43"/>
+      <c r="S50" s="43"/>
+      <c r="T50" s="43"/>
+      <c r="U50" s="43"/>
+      <c r="V50" s="43"/>
+      <c r="W50" s="43"/>
+      <c r="X50" s="43"/>
+    </row>
+    <row r="51" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="50"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="43"/>
+      <c r="L51" s="43"/>
+      <c r="M51" s="43"/>
+      <c r="N51" s="47"/>
+      <c r="O51" s="47"/>
+      <c r="P51" s="43"/>
+      <c r="R51" s="43"/>
+      <c r="S51" s="43"/>
+      <c r="T51" s="43"/>
+      <c r="U51" s="43"/>
+      <c r="V51" s="43"/>
+      <c r="W51" s="43"/>
+      <c r="X51" s="43"/>
+    </row>
+    <row r="52" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="50"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="43"/>
+      <c r="L52" s="43"/>
+      <c r="M52" s="43"/>
+      <c r="N52" s="47"/>
+      <c r="O52" s="47"/>
+      <c r="P52" s="43"/>
+      <c r="R52" s="43"/>
+      <c r="S52" s="43"/>
+      <c r="T52" s="43"/>
+      <c r="U52" s="43"/>
+      <c r="V52" s="43"/>
+      <c r="W52" s="43"/>
+      <c r="X52" s="43"/>
+    </row>
+    <row r="53" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="50"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43"/>
+      <c r="L53" s="43"/>
+      <c r="M53" s="43"/>
+      <c r="N53" s="47"/>
+      <c r="O53" s="47"/>
+      <c r="P53" s="43"/>
+      <c r="R53" s="43"/>
+      <c r="S53" s="43"/>
+      <c r="T53" s="43"/>
+      <c r="U53" s="43"/>
+      <c r="V53" s="43"/>
+      <c r="W53" s="43"/>
+      <c r="X53" s="43"/>
+    </row>
+    <row r="54" spans="1:24" s="44" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="50"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="43"/>
+      <c r="L54" s="43"/>
+      <c r="M54" s="43"/>
+      <c r="N54" s="47"/>
+      <c r="O54" s="47"/>
+      <c r="P54" s="43"/>
+      <c r="R54" s="43"/>
+      <c r="S54" s="43"/>
+      <c r="T54" s="43"/>
+      <c r="U54" s="43"/>
+      <c r="V54" s="43"/>
+      <c r="W54" s="43"/>
+      <c r="X54" s="43"/>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="A55" s="50"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="N55" s="47"/>
+      <c r="O55" s="47"/>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="A56" s="53"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="44"/>
+      <c r="D56" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="E56" s="47"/>
+      <c r="G56" s="44"/>
+      <c r="N56" s="47"/>
+      <c r="O56" s="47"/>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="A57" s="53"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="G57" s="44"/>
+      <c r="N57" s="47"/>
+      <c r="O57" s="47"/>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="A58" s="53"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="G58" s="44"/>
+      <c r="N58" s="47"/>
+      <c r="O58" s="47"/>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="A59" s="53"/>
+      <c r="B59" s="44"/>
+      <c r="C59" s="44"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="G59" s="44"/>
+      <c r="N59" s="47"/>
+      <c r="O59" s="47"/>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="A60" s="53"/>
+      <c r="B60" s="44"/>
+      <c r="C60" s="44"/>
+      <c r="D60" s="44"/>
+      <c r="E60" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="G60" s="44"/>
+      <c r="N60" s="47"/>
+      <c r="O60" s="47"/>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="A61" s="53"/>
+      <c r="B61" s="44"/>
+      <c r="C61" s="44"/>
+      <c r="D61" s="44"/>
+      <c r="E61" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="G61" s="44"/>
+      <c r="N61" s="47"/>
+      <c r="O61" s="47"/>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="A62" s="53"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="44"/>
+      <c r="D62" s="44"/>
+      <c r="E62" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="G62" s="44"/>
+      <c r="N62" s="47"/>
+      <c r="O62" s="47"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="A63" s="53"/>
+      <c r="B63" s="44"/>
+      <c r="C63" s="44"/>
+      <c r="D63" s="44"/>
+      <c r="E63" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="G63" s="44"/>
+      <c r="N63" s="47"/>
+      <c r="O63" s="47"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.15">
+      <c r="A64" s="53"/>
+      <c r="B64" s="44"/>
+      <c r="C64" s="44"/>
+      <c r="D64" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="E64" s="44"/>
+      <c r="G64" s="44"/>
+      <c r="N64" s="47"/>
+      <c r="O64" s="47"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A65" s="53"/>
+      <c r="B65" s="44"/>
+      <c r="E65" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="G65" s="44"/>
+      <c r="N65" s="47"/>
+      <c r="O65" s="47"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A66" s="53"/>
+      <c r="B66" s="44"/>
+      <c r="E66" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="G66" s="44"/>
+      <c r="N66" s="47"/>
+      <c r="O66" s="47"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A67" s="53"/>
+      <c r="B67" s="44"/>
+      <c r="E67" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="G67" s="44"/>
+      <c r="N67" s="47"/>
+      <c r="O67" s="47"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A68" s="53"/>
+      <c r="B68" s="44"/>
+      <c r="E68" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="G68" s="44"/>
+      <c r="N68" s="47"/>
+      <c r="O68" s="47"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A69" s="53"/>
+      <c r="B69" s="44"/>
+      <c r="E69" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="G69" s="44"/>
+      <c r="N69" s="47"/>
+      <c r="O69" s="47"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A70" s="53"/>
+      <c r="B70" s="44"/>
+      <c r="E70" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="G70" s="44"/>
+      <c r="N70" s="47"/>
+      <c r="O70" s="47"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A71" s="53"/>
+      <c r="B71" s="44"/>
+      <c r="E71" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="G71" s="44"/>
+      <c r="N71" s="47"/>
+      <c r="O71" s="47"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A72" s="53"/>
+      <c r="B72" s="44"/>
+      <c r="E72" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="G72" s="44"/>
+      <c r="N72" s="47"/>
+      <c r="O72" s="47"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A73" s="53"/>
+      <c r="B73" s="44"/>
+      <c r="E73" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="G73" s="44"/>
+      <c r="N73" s="47"/>
+      <c r="O73" s="47"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A74" s="53"/>
+      <c r="B74" s="44"/>
+      <c r="E74" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="G74" s="44"/>
+      <c r="N74" s="47"/>
+      <c r="O74" s="47"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A75" s="53"/>
+      <c r="B75" s="44"/>
+      <c r="E75" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="G75" s="44"/>
+      <c r="N75" s="47"/>
+      <c r="O75" s="47"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A76" s="53"/>
+      <c r="B76" s="44"/>
+      <c r="C76" s="44"/>
+      <c r="D76" s="44"/>
+      <c r="E76" s="47"/>
+      <c r="G76" s="44"/>
+      <c r="N76" s="47"/>
+      <c r="O76" s="47"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A77" s="54"/>
+      <c r="C77" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="N77" s="47"/>
+      <c r="O77" s="47"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A78" s="54"/>
+      <c r="C78" s="55"/>
+      <c r="D78" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="N78" s="47"/>
+      <c r="O78" s="47"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A79" s="54"/>
+      <c r="C79" s="55"/>
+      <c r="D79" s="44"/>
+      <c r="E79" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="N79" s="47"/>
+      <c r="O79" s="47"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A80" s="54"/>
+      <c r="C80" s="55"/>
+      <c r="D80" s="44"/>
+      <c r="E80" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="N80" s="47"/>
+      <c r="O80" s="47"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A81" s="54"/>
+      <c r="C81" s="55"/>
+      <c r="D81" s="44"/>
+      <c r="E81" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="N81" s="47"/>
+      <c r="O81" s="47"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A82" s="54"/>
+      <c r="C82" s="55"/>
+      <c r="D82" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="N82" s="47"/>
+      <c r="O82" s="47"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A83" s="54"/>
+      <c r="C83" s="55"/>
+      <c r="D83" s="44"/>
+      <c r="E83" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="N83" s="47"/>
+      <c r="O83" s="47"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A84" s="54"/>
+      <c r="C84" s="55"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="N84" s="47"/>
+      <c r="O84" s="47"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A85" s="54"/>
+      <c r="C85" s="55"/>
+      <c r="D85" s="44"/>
+      <c r="E85" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="N85" s="47"/>
+      <c r="O85" s="47"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A86" s="54"/>
+      <c r="C86" s="55"/>
+      <c r="D86" s="44"/>
+      <c r="E86" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="N86" s="47"/>
+      <c r="O86" s="47"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A87" s="54"/>
+      <c r="C87" s="55"/>
+      <c r="D87" s="44"/>
+      <c r="E87" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="N87" s="47"/>
+      <c r="O87" s="47"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A88" s="54"/>
+      <c r="C88" s="55"/>
+      <c r="D88" s="44"/>
+      <c r="E88" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="N88" s="47"/>
+      <c r="O88" s="47"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A89" s="53"/>
+      <c r="D89" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="F89" s="44"/>
+      <c r="N89" s="47"/>
+      <c r="O89" s="47"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A90" s="53"/>
+      <c r="D90" s="44"/>
+      <c r="E90" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="F90" s="44"/>
+      <c r="N90" s="47"/>
+      <c r="O90" s="47"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A91" s="53"/>
+      <c r="D91" s="44"/>
+      <c r="E91" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="F91" s="44"/>
+      <c r="N91" s="47"/>
+      <c r="O91" s="47"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A92" s="53"/>
+      <c r="D92" s="44"/>
+      <c r="E92" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="F92" s="44"/>
+      <c r="N92" s="47"/>
+      <c r="O92" s="47"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A93" s="53"/>
+      <c r="D93" s="44"/>
+      <c r="E93" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="F93" s="44"/>
+      <c r="N93" s="47"/>
+      <c r="O93" s="47"/>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A94" s="53"/>
+      <c r="D94" s="44"/>
+      <c r="E94" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="F94" s="44"/>
+      <c r="N94" s="47"/>
+      <c r="O94" s="47"/>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A95" s="53"/>
+      <c r="D95" s="44"/>
+      <c r="E95" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="F95" s="44"/>
+      <c r="N95" s="47"/>
+      <c r="O95" s="47"/>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A96" s="53"/>
+      <c r="D96" s="44"/>
+      <c r="E96" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="F96" s="44"/>
+      <c r="N96" s="47"/>
+      <c r="O96" s="47"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A97" s="53"/>
+      <c r="D97" s="44"/>
+      <c r="E97" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="F97" s="44"/>
+      <c r="N97" s="47"/>
+      <c r="O97" s="47"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A98" s="53"/>
+      <c r="C98" s="44"/>
+      <c r="D98" s="47"/>
+      <c r="E98" s="47"/>
+      <c r="N98" s="47"/>
+      <c r="O98" s="47"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A99" s="53"/>
+      <c r="C99" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="O99" s="47"/>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A100" s="53"/>
+      <c r="D100" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="N100" s="47"/>
+      <c r="O100" s="47"/>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A101" s="53"/>
+      <c r="D101" s="44"/>
+      <c r="E101" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="N101" s="47"/>
+      <c r="O101" s="47"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A102" s="53"/>
+      <c r="D102" s="44"/>
+      <c r="E102" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="N102" s="47"/>
+      <c r="O102" s="47"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A103" s="53"/>
+      <c r="D103" s="44"/>
+      <c r="E103" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="N103" s="47"/>
+      <c r="O103" s="47"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A104" s="53"/>
+      <c r="D104" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="N104" s="47"/>
+      <c r="O104" s="47"/>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A105" s="53"/>
+      <c r="E105" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="N105" s="47"/>
+      <c r="O105" s="47"/>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A106" s="53"/>
+      <c r="E106" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="N106" s="47"/>
+      <c r="O106" s="47"/>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A107" s="53"/>
+      <c r="E107" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="N107" s="47"/>
+      <c r="O107" s="47"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A108" s="53"/>
+      <c r="D108" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="N108" s="47"/>
+      <c r="O108" s="47"/>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A109" s="53"/>
+      <c r="E109" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="N109" s="47"/>
+      <c r="O109" s="47"/>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A110" s="53"/>
+      <c r="E110" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="N110" s="47"/>
+      <c r="O110" s="47"/>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A111" s="53"/>
+      <c r="E111" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="N111" s="47"/>
+      <c r="O111" s="47"/>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A112" s="53"/>
+      <c r="E112" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="N112" s="47"/>
+      <c r="O112" s="47"/>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A113" s="53"/>
+      <c r="D113" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="N113" s="47"/>
+      <c r="O113" s="47"/>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A114" s="53"/>
+      <c r="E114" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="N114" s="47"/>
+      <c r="O114" s="47"/>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A115" s="53"/>
+      <c r="E115" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="N115" s="47"/>
+      <c r="O115" s="47"/>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A116" s="53"/>
+      <c r="E116" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="N116" s="47"/>
+      <c r="O116" s="47"/>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A117" s="53"/>
+      <c r="E117" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="N117" s="47"/>
+      <c r="O117" s="47"/>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A118" s="54"/>
+      <c r="D118" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="N118" s="47"/>
+      <c r="O118" s="47"/>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A119" s="54"/>
+      <c r="E119" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="N119" s="47"/>
+      <c r="O119" s="47"/>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A120" s="54"/>
+      <c r="E120" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="N120" s="47"/>
+      <c r="O120" s="47"/>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A121" s="54"/>
+      <c r="E121" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="N121" s="47"/>
+      <c r="O121" s="47"/>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A122" s="53"/>
+      <c r="D122" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="N122" s="47"/>
+      <c r="O122" s="47"/>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A123" s="53"/>
+      <c r="E123" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="N123" s="47"/>
+      <c r="O123" s="47"/>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A124" s="53"/>
+      <c r="E124" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="N124" s="47"/>
+      <c r="O124" s="47"/>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A125" s="53"/>
+      <c r="D125" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="O22" s="49"/>
-      <c r="P22" s="49"/>
-    </row>
-    <row r="23" spans="1:16" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="48"/>
-      <c r="B23" s="52"/>
-      <c r="E23" s="46" t="s">
+      <c r="N125" s="47"/>
+      <c r="O125" s="47"/>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A126" s="53"/>
+      <c r="E126" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="O23" s="49"/>
-      <c r="P23" s="49"/>
-    </row>
-    <row r="24" spans="1:16" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="48"/>
-      <c r="B24" s="52"/>
-      <c r="E24" s="46" t="s">
+      <c r="N126" s="47"/>
+      <c r="O126" s="47"/>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A127" s="53"/>
+      <c r="E127" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="O24" s="49"/>
-      <c r="P24" s="49"/>
-    </row>
-    <row r="25" spans="1:16" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="48"/>
-      <c r="B25" s="52"/>
-      <c r="E25" s="46" t="s">
+      <c r="N127" s="47"/>
+      <c r="O127" s="47"/>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A128" s="53"/>
+      <c r="D128" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="O25" s="49"/>
-      <c r="P25" s="49"/>
-    </row>
-    <row r="26" spans="1:16" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="48"/>
-      <c r="B26" s="52"/>
-      <c r="E26" s="46" t="s">
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A129" s="53"/>
+      <c r="E129" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="O26" s="49"/>
-      <c r="P26" s="49"/>
-    </row>
-    <row r="27" spans="1:16" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="48"/>
-      <c r="B27" s="52"/>
-      <c r="E27" s="46" t="s">
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A130" s="53"/>
+      <c r="E130" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="O27" s="49"/>
-      <c r="P27" s="49"/>
-    </row>
-    <row r="28" spans="1:16" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="48"/>
-      <c r="B28" s="52"/>
-      <c r="E28" s="46" t="s">
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A131" s="53"/>
+      <c r="E131" s="43" t="s">
         <v>145</v>
       </c>
-      <c r="O28" s="49"/>
-      <c r="P28" s="49"/>
-    </row>
-    <row r="29" spans="1:16" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="48"/>
-      <c r="B29" s="52"/>
-      <c r="E29" s="46" t="s">
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A132" s="53"/>
+      <c r="D132" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="O29" s="49"/>
-      <c r="P29" s="49"/>
-    </row>
-    <row r="30" spans="1:16" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="48"/>
-      <c r="D30" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="O30" s="49"/>
-    </row>
-    <row r="31" spans="1:16" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="48"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="O31" s="49"/>
-    </row>
-    <row r="32" spans="1:16" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="48"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="O32" s="49"/>
-    </row>
-    <row r="33" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="48"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="O33" s="49"/>
-    </row>
-    <row r="34" spans="1:24" s="46" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="48"/>
-      <c r="O34" s="49"/>
-      <c r="P34" s="49"/>
-    </row>
-    <row r="35" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="53"/>
-      <c r="B35" s="54"/>
-      <c r="C35" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="45"/>
-      <c r="O35" s="49"/>
-      <c r="P35" s="49"/>
-      <c r="R35" s="55"/>
-      <c r="S35" s="55"/>
-      <c r="T35" s="55"/>
-      <c r="U35" s="55"/>
-      <c r="V35" s="55"/>
-      <c r="W35" s="55"/>
-      <c r="X35" s="55"/>
-    </row>
-    <row r="36" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="53"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="49"/>
-      <c r="O36" s="49"/>
-      <c r="P36" s="55"/>
-      <c r="R36" s="55"/>
-      <c r="S36" s="55"/>
-      <c r="T36" s="55"/>
-      <c r="U36" s="55"/>
-      <c r="V36" s="55"/>
-      <c r="W36" s="55"/>
-      <c r="X36" s="55"/>
-    </row>
-    <row r="37" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="53"/>
-      <c r="B37" s="52"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="55"/>
-      <c r="K37" s="55"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="55"/>
-      <c r="N37" s="49"/>
-      <c r="O37" s="49"/>
-      <c r="P37" s="55"/>
-      <c r="R37" s="55"/>
-      <c r="S37" s="55"/>
-      <c r="T37" s="55"/>
-      <c r="U37" s="55"/>
-      <c r="V37" s="55"/>
-      <c r="W37" s="55"/>
-      <c r="X37" s="55"/>
-    </row>
-    <row r="38" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="53"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="55" t="s">
-        <v>68</v>
-      </c>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="55"/>
-      <c r="L38" s="55"/>
-      <c r="M38" s="55"/>
-      <c r="N38" s="49"/>
-      <c r="O38" s="49"/>
-      <c r="P38" s="55"/>
-      <c r="R38" s="55"/>
-      <c r="S38" s="55"/>
-      <c r="T38" s="55"/>
-      <c r="U38" s="55"/>
-      <c r="V38" s="55"/>
-      <c r="W38" s="55"/>
-      <c r="X38" s="55"/>
-    </row>
-    <row r="39" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="53"/>
-      <c r="B39" s="52"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="55" t="s">
-        <v>69</v>
-      </c>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
-      <c r="K39" s="55"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="55"/>
-      <c r="N39" s="49"/>
-      <c r="O39" s="49"/>
-      <c r="P39" s="55"/>
-      <c r="R39" s="55"/>
-      <c r="S39" s="55"/>
-      <c r="T39" s="55"/>
-      <c r="U39" s="55"/>
-      <c r="V39" s="55"/>
-      <c r="W39" s="55"/>
-      <c r="X39" s="55"/>
-    </row>
-    <row r="40" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="53"/>
-      <c r="B40" s="52"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="55"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="55"/>
-      <c r="N40" s="49"/>
-      <c r="O40" s="49"/>
-      <c r="P40" s="55"/>
-      <c r="R40" s="55"/>
-      <c r="S40" s="55"/>
-      <c r="T40" s="55"/>
-      <c r="U40" s="55"/>
-      <c r="V40" s="55"/>
-      <c r="W40" s="55"/>
-      <c r="X40" s="55"/>
-    </row>
-    <row r="41" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="53"/>
-      <c r="B41" s="52"/>
-      <c r="C41" s="45"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="F41" s="55"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="55"/>
-      <c r="J41" s="55"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="55"/>
-      <c r="N41" s="49"/>
-      <c r="O41" s="49"/>
-      <c r="P41" s="55"/>
-      <c r="R41" s="55"/>
-      <c r="S41" s="55"/>
-      <c r="T41" s="55"/>
-      <c r="U41" s="55"/>
-      <c r="V41" s="55"/>
-      <c r="W41" s="55"/>
-      <c r="X41" s="55"/>
-    </row>
-    <row r="42" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="53"/>
-      <c r="B42" s="52"/>
-      <c r="C42" s="45"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="F42" s="55"/>
-      <c r="G42" s="55"/>
-      <c r="H42" s="55"/>
-      <c r="I42" s="55"/>
-      <c r="J42" s="55"/>
-      <c r="K42" s="55"/>
-      <c r="L42" s="55"/>
-      <c r="M42" s="55"/>
-      <c r="N42" s="49"/>
-      <c r="O42" s="49"/>
-      <c r="P42" s="55"/>
-      <c r="R42" s="55"/>
-      <c r="S42" s="55"/>
-      <c r="T42" s="55"/>
-      <c r="U42" s="55"/>
-      <c r="V42" s="55"/>
-      <c r="W42" s="55"/>
-      <c r="X42" s="55"/>
-    </row>
-    <row r="43" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="53"/>
-      <c r="B43" s="52"/>
-      <c r="C43" s="45"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="55" t="s">
-        <v>73</v>
-      </c>
-      <c r="F43" s="55"/>
-      <c r="G43" s="55"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="55"/>
-      <c r="J43" s="55"/>
-      <c r="K43" s="55"/>
-      <c r="L43" s="55"/>
-      <c r="M43" s="55"/>
-      <c r="N43" s="49"/>
-      <c r="O43" s="49"/>
-      <c r="P43" s="55"/>
-      <c r="R43" s="55"/>
-      <c r="S43" s="55"/>
-      <c r="T43" s="55"/>
-      <c r="U43" s="55"/>
-      <c r="V43" s="55"/>
-      <c r="W43" s="55"/>
-      <c r="X43" s="55"/>
-    </row>
-    <row r="44" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="53"/>
-      <c r="B44" s="56"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="E44" s="55"/>
-      <c r="F44" s="55"/>
-      <c r="G44" s="55"/>
-      <c r="H44" s="55"/>
-      <c r="I44" s="55"/>
-      <c r="J44" s="55"/>
-      <c r="K44" s="55"/>
-      <c r="L44" s="55"/>
-      <c r="M44" s="55"/>
-      <c r="N44" s="49"/>
-      <c r="O44" s="49"/>
-      <c r="P44" s="55"/>
-      <c r="R44" s="55"/>
-      <c r="S44" s="55"/>
-      <c r="T44" s="55"/>
-      <c r="U44" s="55"/>
-      <c r="V44" s="55"/>
-      <c r="W44" s="55"/>
-      <c r="X44" s="55"/>
-    </row>
-    <row r="45" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="53"/>
-      <c r="B45" s="56"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="F45" s="55"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="55"/>
-      <c r="J45" s="55"/>
-      <c r="K45" s="55"/>
-      <c r="L45" s="55"/>
-      <c r="M45" s="55"/>
-      <c r="N45" s="49"/>
-      <c r="O45" s="49"/>
-      <c r="P45" s="55"/>
-      <c r="R45" s="55"/>
-      <c r="S45" s="55"/>
-      <c r="T45" s="55"/>
-      <c r="U45" s="55"/>
-      <c r="V45" s="55"/>
-      <c r="W45" s="55"/>
-      <c r="X45" s="55"/>
-    </row>
-    <row r="46" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="53"/>
-      <c r="B46" s="56"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="55" t="s">
-        <v>75</v>
-      </c>
-      <c r="F46" s="55"/>
-      <c r="G46" s="55"/>
-      <c r="H46" s="55"/>
-      <c r="I46" s="55"/>
-      <c r="J46" s="55"/>
-      <c r="K46" s="55"/>
-      <c r="L46" s="55"/>
-      <c r="M46" s="55"/>
-      <c r="N46" s="49"/>
-      <c r="O46" s="49"/>
-      <c r="P46" s="55"/>
-      <c r="R46" s="55"/>
-      <c r="S46" s="55"/>
-      <c r="T46" s="55"/>
-      <c r="U46" s="55"/>
-      <c r="V46" s="55"/>
-      <c r="W46" s="55"/>
-      <c r="X46" s="55"/>
-    </row>
-    <row r="47" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="53"/>
-      <c r="B47" s="56"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="55" t="s">
-        <v>76</v>
-      </c>
-      <c r="F47" s="55"/>
-      <c r="G47" s="55"/>
-      <c r="H47" s="55"/>
-      <c r="I47" s="55"/>
-      <c r="J47" s="55"/>
-      <c r="K47" s="55"/>
-      <c r="L47" s="55"/>
-      <c r="M47" s="55"/>
-      <c r="N47" s="49"/>
-      <c r="O47" s="49"/>
-      <c r="P47" s="55"/>
-      <c r="R47" s="55"/>
-      <c r="S47" s="55"/>
-      <c r="T47" s="55"/>
-      <c r="U47" s="55"/>
-      <c r="V47" s="55"/>
-      <c r="W47" s="55"/>
-      <c r="X47" s="55"/>
-    </row>
-    <row r="48" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="53"/>
-      <c r="B48" s="56"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="F48" s="55"/>
-      <c r="G48" s="55"/>
-      <c r="H48" s="55"/>
-      <c r="I48" s="55"/>
-      <c r="J48" s="55"/>
-      <c r="K48" s="55"/>
-      <c r="L48" s="55"/>
-      <c r="M48" s="55"/>
-      <c r="N48" s="49"/>
-      <c r="O48" s="49"/>
-      <c r="P48" s="55"/>
-      <c r="R48" s="55"/>
-      <c r="S48" s="55"/>
-      <c r="T48" s="55"/>
-      <c r="U48" s="55"/>
-      <c r="V48" s="55"/>
-      <c r="W48" s="55"/>
-      <c r="X48" s="55"/>
-    </row>
-    <row r="49" spans="1:24" s="46" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="53"/>
-      <c r="B49" s="56"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="55"/>
-      <c r="G49" s="55"/>
-      <c r="H49" s="55"/>
-      <c r="I49" s="55"/>
-      <c r="J49" s="55"/>
-      <c r="K49" s="55"/>
-      <c r="L49" s="55"/>
-      <c r="M49" s="55"/>
-      <c r="N49" s="49"/>
-      <c r="O49" s="49"/>
-      <c r="P49" s="55"/>
-      <c r="R49" s="55"/>
-      <c r="S49" s="55"/>
-      <c r="T49" s="55"/>
-      <c r="U49" s="55"/>
-      <c r="V49" s="55"/>
-      <c r="W49" s="55"/>
-      <c r="X49" s="55"/>
-    </row>
-    <row r="50" spans="1:24" s="55" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="53"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="45"/>
-      <c r="K50" s="45"/>
-      <c r="L50" s="45"/>
-      <c r="M50" s="45"/>
-      <c r="N50" s="49"/>
-      <c r="O50" s="49"/>
-      <c r="P50" s="45"/>
-      <c r="R50" s="45"/>
-      <c r="S50" s="45"/>
-      <c r="T50" s="45"/>
-      <c r="U50" s="45"/>
-      <c r="V50" s="45"/>
-      <c r="W50" s="45"/>
-      <c r="X50" s="45"/>
-    </row>
-    <row r="51" spans="1:24" s="55" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="57"/>
-      <c r="B51" s="46"/>
-      <c r="C51" s="46"/>
-      <c r="D51" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="E51" s="49"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="45"/>
-      <c r="I51" s="45"/>
-      <c r="J51" s="45"/>
-      <c r="K51" s="45"/>
-      <c r="L51" s="45"/>
-      <c r="M51" s="45"/>
-      <c r="N51" s="49"/>
-      <c r="O51" s="49"/>
-      <c r="P51" s="45"/>
-      <c r="R51" s="45"/>
-      <c r="S51" s="45"/>
-      <c r="T51" s="45"/>
-      <c r="U51" s="45"/>
-      <c r="V51" s="45"/>
-      <c r="W51" s="45"/>
-      <c r="X51" s="45"/>
-    </row>
-    <row r="52" spans="1:24" s="55" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="57"/>
-      <c r="B52" s="46"/>
-      <c r="C52" s="46"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="46" t="s">
-        <v>78</v>
-      </c>
-      <c r="G52" s="46"/>
-      <c r="H52" s="45"/>
-      <c r="I52" s="45"/>
-      <c r="J52" s="45"/>
-      <c r="K52" s="45"/>
-      <c r="L52" s="45"/>
-      <c r="M52" s="45"/>
-      <c r="N52" s="49"/>
-      <c r="O52" s="49"/>
-      <c r="P52" s="45"/>
-      <c r="R52" s="45"/>
-      <c r="S52" s="45"/>
-      <c r="T52" s="45"/>
-      <c r="U52" s="45"/>
-      <c r="V52" s="45"/>
-      <c r="W52" s="45"/>
-      <c r="X52" s="45"/>
-    </row>
-    <row r="53" spans="1:24" s="55" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="57"/>
-      <c r="B53" s="46"/>
-      <c r="C53" s="46"/>
-      <c r="D53" s="46"/>
-      <c r="E53" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="G53" s="46"/>
-      <c r="H53" s="45"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="45"/>
-      <c r="K53" s="45"/>
-      <c r="L53" s="45"/>
-      <c r="M53" s="45"/>
-      <c r="N53" s="49"/>
-      <c r="O53" s="49"/>
-      <c r="P53" s="45"/>
-      <c r="R53" s="45"/>
-      <c r="S53" s="45"/>
-      <c r="T53" s="45"/>
-      <c r="U53" s="45"/>
-      <c r="V53" s="45"/>
-      <c r="W53" s="45"/>
-      <c r="X53" s="45"/>
-    </row>
-    <row r="54" spans="1:24" s="55" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="57"/>
-      <c r="B54" s="46"/>
-      <c r="C54" s="46"/>
-      <c r="D54" s="46"/>
-      <c r="E54" s="46" t="s">
-        <v>80</v>
-      </c>
-      <c r="G54" s="46"/>
-      <c r="H54" s="45"/>
-      <c r="I54" s="45"/>
-      <c r="J54" s="45"/>
-      <c r="K54" s="45"/>
-      <c r="L54" s="45"/>
-      <c r="M54" s="45"/>
-      <c r="N54" s="49"/>
-      <c r="O54" s="49"/>
-      <c r="P54" s="45"/>
-      <c r="R54" s="45"/>
-      <c r="S54" s="45"/>
-      <c r="T54" s="45"/>
-      <c r="U54" s="45"/>
-      <c r="V54" s="45"/>
-      <c r="W54" s="45"/>
-      <c r="X54" s="45"/>
-    </row>
-    <row r="55" spans="1:24" s="55" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="57"/>
-      <c r="B55" s="46"/>
-      <c r="C55" s="46"/>
-      <c r="D55" s="46"/>
-      <c r="E55" s="46" t="s">
-        <v>81</v>
-      </c>
-      <c r="G55" s="46"/>
-      <c r="H55" s="45"/>
-      <c r="I55" s="45"/>
-      <c r="J55" s="45"/>
-      <c r="K55" s="45"/>
-      <c r="L55" s="45"/>
-      <c r="M55" s="45"/>
-      <c r="N55" s="49"/>
-      <c r="O55" s="49"/>
-      <c r="P55" s="45"/>
-      <c r="R55" s="45"/>
-      <c r="S55" s="45"/>
-      <c r="T55" s="45"/>
-      <c r="U55" s="45"/>
-      <c r="V55" s="45"/>
-      <c r="W55" s="45"/>
-      <c r="X55" s="45"/>
-    </row>
-    <row r="56" spans="1:24" s="55" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="57"/>
-      <c r="B56" s="46"/>
-      <c r="C56" s="46"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="G56" s="46"/>
-      <c r="H56" s="45"/>
-      <c r="I56" s="45"/>
-      <c r="J56" s="45"/>
-      <c r="K56" s="45"/>
-      <c r="L56" s="45"/>
-      <c r="M56" s="45"/>
-      <c r="N56" s="49"/>
-      <c r="O56" s="49"/>
-      <c r="P56" s="45"/>
-      <c r="R56" s="45"/>
-      <c r="S56" s="45"/>
-      <c r="T56" s="45"/>
-      <c r="U56" s="45"/>
-      <c r="V56" s="45"/>
-      <c r="W56" s="45"/>
-      <c r="X56" s="45"/>
-    </row>
-    <row r="57" spans="1:24" s="55" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="57"/>
-      <c r="B57" s="46"/>
-      <c r="C57" s="46"/>
-      <c r="D57" s="46"/>
-      <c r="E57" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="G57" s="46"/>
-      <c r="H57" s="45"/>
-      <c r="I57" s="45"/>
-      <c r="J57" s="45"/>
-      <c r="K57" s="45"/>
-      <c r="L57" s="45"/>
-      <c r="M57" s="45"/>
-      <c r="N57" s="49"/>
-      <c r="O57" s="49"/>
-      <c r="P57" s="45"/>
-      <c r="R57" s="45"/>
-      <c r="S57" s="45"/>
-      <c r="T57" s="45"/>
-      <c r="U57" s="45"/>
-      <c r="V57" s="45"/>
-      <c r="W57" s="45"/>
-      <c r="X57" s="45"/>
-    </row>
-    <row r="58" spans="1:24" s="55" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="57"/>
-      <c r="B58" s="46"/>
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46" t="s">
-        <v>84</v>
-      </c>
-      <c r="G58" s="46"/>
-      <c r="H58" s="45"/>
-      <c r="I58" s="45"/>
-      <c r="J58" s="45"/>
-      <c r="K58" s="45"/>
-      <c r="L58" s="45"/>
-      <c r="M58" s="45"/>
-      <c r="N58" s="49"/>
-      <c r="O58" s="49"/>
-      <c r="P58" s="45"/>
-      <c r="R58" s="45"/>
-      <c r="S58" s="45"/>
-      <c r="T58" s="45"/>
-      <c r="U58" s="45"/>
-      <c r="V58" s="45"/>
-      <c r="W58" s="45"/>
-      <c r="X58" s="45"/>
-    </row>
-    <row r="59" spans="1:24" s="55" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="57"/>
-      <c r="B59" s="46"/>
-      <c r="C59" s="46"/>
-      <c r="D59" s="46"/>
-      <c r="E59" s="49"/>
-      <c r="G59" s="46"/>
-      <c r="H59" s="45"/>
-      <c r="I59" s="45"/>
-      <c r="J59" s="45"/>
-      <c r="K59" s="45"/>
-      <c r="L59" s="45"/>
-      <c r="M59" s="45"/>
-      <c r="N59" s="49"/>
-      <c r="O59" s="49"/>
-      <c r="P59" s="45"/>
-      <c r="R59" s="45"/>
-      <c r="S59" s="45"/>
-      <c r="T59" s="45"/>
-      <c r="U59" s="45"/>
-      <c r="V59" s="45"/>
-      <c r="W59" s="45"/>
-      <c r="X59" s="45"/>
-    </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.15">
-      <c r="A60" s="58"/>
-      <c r="C60" s="59" t="s">
-        <v>35</v>
-      </c>
-      <c r="N60" s="49"/>
-      <c r="O60" s="49"/>
-    </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.15">
-      <c r="A61" s="58"/>
-      <c r="C61" s="59"/>
-      <c r="D61" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="N61" s="49"/>
-      <c r="O61" s="49"/>
-    </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.15">
-      <c r="A62" s="58"/>
-      <c r="C62" s="59"/>
-      <c r="D62" s="46"/>
-      <c r="E62" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="N62" s="49"/>
-      <c r="O62" s="49"/>
-    </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.15">
-      <c r="A63" s="58"/>
-      <c r="C63" s="59"/>
-      <c r="D63" s="46"/>
-      <c r="E63" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="N63" s="49"/>
-      <c r="O63" s="49"/>
-    </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.15">
-      <c r="A64" s="58"/>
-      <c r="C64" s="59"/>
-      <c r="D64" s="46"/>
-      <c r="E64" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="N64" s="49"/>
-      <c r="O64" s="49"/>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A65" s="58"/>
-      <c r="C65" s="59"/>
-      <c r="D65" s="46" t="s">
-        <v>37</v>
-      </c>
-      <c r="N65" s="49"/>
-      <c r="O65" s="49"/>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A66" s="58"/>
-      <c r="C66" s="59"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="N66" s="49"/>
-      <c r="O66" s="49"/>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A67" s="58"/>
-      <c r="C67" s="59"/>
-      <c r="D67" s="46"/>
-      <c r="E67" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="N67" s="49"/>
-      <c r="O67" s="49"/>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A68" s="58"/>
-      <c r="C68" s="59"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="N68" s="49"/>
-      <c r="O68" s="49"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A69" s="58"/>
-      <c r="C69" s="59"/>
-      <c r="D69" s="46"/>
-      <c r="E69" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="N69" s="49"/>
-      <c r="O69" s="49"/>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A70" s="58"/>
-      <c r="C70" s="59"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="N70" s="49"/>
-      <c r="O70" s="49"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A71" s="58"/>
-      <c r="C71" s="59"/>
-      <c r="D71" s="46"/>
-      <c r="E71" s="45" t="s">
-        <v>93</v>
-      </c>
-      <c r="N71" s="49"/>
-      <c r="O71" s="49"/>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A72" s="60"/>
-      <c r="D72" s="46" t="s">
-        <v>38</v>
-      </c>
-      <c r="F72" s="46"/>
-      <c r="N72" s="49"/>
-      <c r="O72" s="49"/>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A73" s="60"/>
-      <c r="D73" s="46"/>
-      <c r="E73" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F73" s="46"/>
-      <c r="N73" s="49"/>
-      <c r="O73" s="49"/>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A74" s="60"/>
-      <c r="D74" s="46"/>
-      <c r="E74" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F74" s="46"/>
-      <c r="N74" s="49"/>
-      <c r="O74" s="49"/>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A75" s="60"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="45" t="s">
-        <v>96</v>
-      </c>
-      <c r="F75" s="46"/>
-      <c r="N75" s="49"/>
-      <c r="O75" s="49"/>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A76" s="60"/>
-      <c r="D76" s="46"/>
-      <c r="E76" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="F76" s="46"/>
-      <c r="N76" s="49"/>
-      <c r="O76" s="49"/>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A77" s="60"/>
-      <c r="D77" s="46"/>
-      <c r="E77" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="F77" s="46"/>
-      <c r="N77" s="49"/>
-      <c r="O77" s="49"/>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A78" s="60"/>
-      <c r="D78" s="46"/>
-      <c r="E78" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="F78" s="46"/>
-      <c r="N78" s="49"/>
-      <c r="O78" s="49"/>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A79" s="60"/>
-      <c r="D79" s="46"/>
-      <c r="E79" s="45" t="s">
-        <v>100</v>
-      </c>
-      <c r="F79" s="46"/>
-      <c r="N79" s="49"/>
-      <c r="O79" s="49"/>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A80" s="60"/>
-      <c r="D80" s="46"/>
-      <c r="E80" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="F80" s="46"/>
-      <c r="N80" s="49"/>
-      <c r="O80" s="49"/>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A81" s="60"/>
-      <c r="C81" s="46"/>
-      <c r="D81" s="49"/>
-      <c r="E81" s="49"/>
-      <c r="N81" s="49"/>
-      <c r="O81" s="49"/>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A82" s="60"/>
-      <c r="C82" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="O82" s="49"/>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A83" s="60"/>
-      <c r="D83" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="N83" s="49"/>
-      <c r="O83" s="49"/>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A84" s="60"/>
-      <c r="D84" s="46"/>
-      <c r="E84" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="N84" s="49"/>
-      <c r="O84" s="49"/>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A85" s="60"/>
-      <c r="D85" s="46"/>
-      <c r="E85" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="N85" s="49"/>
-      <c r="O85" s="49"/>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A86" s="60"/>
-      <c r="D86" s="46"/>
-      <c r="E86" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="N86" s="49"/>
-      <c r="O86" s="49"/>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A87" s="60"/>
-      <c r="D87" s="55" t="s">
-        <v>41</v>
-      </c>
-      <c r="N87" s="49"/>
-      <c r="O87" s="49"/>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A88" s="60"/>
-      <c r="D88" s="55"/>
-      <c r="E88" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="N88" s="49"/>
-      <c r="O88" s="49"/>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A89" s="60"/>
-      <c r="D89" s="55"/>
-      <c r="E89" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="N89" s="49"/>
-      <c r="O89" s="49"/>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A90" s="60"/>
-      <c r="D90" s="55"/>
-      <c r="E90" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="N90" s="49"/>
-      <c r="O90" s="49"/>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A91" s="60"/>
-      <c r="D91" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="N91" s="49"/>
-      <c r="O91" s="49"/>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A92" s="60"/>
-      <c r="D92" s="55"/>
-      <c r="E92" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="N92" s="49"/>
-      <c r="O92" s="49"/>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A93" s="60"/>
-      <c r="D93" s="55"/>
-      <c r="E93" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="N93" s="49"/>
-      <c r="O93" s="49"/>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A94" s="60"/>
-      <c r="D94" s="55"/>
-      <c r="E94" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="N94" s="49"/>
-      <c r="O94" s="49"/>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A95" s="60"/>
-      <c r="D95" s="55"/>
-      <c r="E95" s="45" t="s">
-        <v>111</v>
-      </c>
-      <c r="N95" s="49"/>
-      <c r="O95" s="49"/>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A96" s="60"/>
-      <c r="D96" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="N96" s="49"/>
-      <c r="O96" s="49"/>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A97" s="60"/>
-      <c r="D97" s="55"/>
-      <c r="E97" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="N97" s="49"/>
-      <c r="O97" s="49"/>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A98" s="60"/>
-      <c r="D98" s="55"/>
-      <c r="E98" s="45" t="s">
-        <v>113</v>
-      </c>
-      <c r="N98" s="49"/>
-      <c r="O98" s="49"/>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A99" s="60"/>
-      <c r="D99" s="55"/>
-      <c r="E99" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="N99" s="49"/>
-      <c r="O99" s="49"/>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A100" s="60"/>
-      <c r="D100" s="55"/>
-      <c r="E100" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="N100" s="49"/>
-      <c r="O100" s="49"/>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A101" s="58"/>
-      <c r="D101" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="N101" s="49"/>
-      <c r="O101" s="49"/>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A102" s="58"/>
-      <c r="E102" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="N102" s="49"/>
-      <c r="O102" s="49"/>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A103" s="58"/>
-      <c r="E103" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="N103" s="49"/>
-      <c r="O103" s="49"/>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A104" s="58"/>
-      <c r="E104" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="N104" s="49"/>
-      <c r="O104" s="49"/>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A105" s="60"/>
-      <c r="D105" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="N105" s="49"/>
-      <c r="O105" s="49"/>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A106" s="60"/>
-      <c r="E106" s="45" t="s">
-        <v>119</v>
-      </c>
-      <c r="N106" s="49"/>
-      <c r="O106" s="49"/>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A107" s="60"/>
-      <c r="E107" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="N107" s="49"/>
-      <c r="O107" s="49"/>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A108" s="60"/>
-      <c r="D108" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="N108" s="49"/>
-      <c r="O108" s="49"/>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A109" s="60"/>
-      <c r="E109" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="N109" s="49"/>
-      <c r="O109" s="49"/>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A110" s="60"/>
-      <c r="E110" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="N110" s="49"/>
-      <c r="O110" s="49"/>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A111" s="60"/>
-      <c r="D111" s="45" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A112" s="60"/>
-      <c r="E112" s="45" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A113" s="60"/>
-      <c r="E113" s="45" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A114" s="60"/>
-      <c r="E114" s="45" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A115" s="60"/>
-      <c r="D115" s="45" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A116" s="60"/>
-      <c r="E116" s="45" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A117" s="60"/>
-      <c r="E117" s="45" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A118" s="60"/>
-      <c r="E118" s="45" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A119" s="60"/>
-      <c r="D119" s="45" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A120" s="60"/>
-      <c r="E120" s="45" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A121" s="60"/>
-      <c r="E121" s="45" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A122" s="60"/>
-      <c r="D122" s="45" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A123" s="60"/>
-      <c r="E123" s="45" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A124" s="60"/>
-      <c r="E124" s="45" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="D125" s="45" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A126" s="58"/>
-      <c r="D126" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="O126" s="49"/>
-      <c r="P126" s="49"/>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="E127" s="45" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="E128" s="45" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="129" spans="5:5" x14ac:dyDescent="0.15">
-      <c r="E129" s="45" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="130" spans="5:5" x14ac:dyDescent="0.15">
-      <c r="E130" s="45" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="131" spans="5:5" x14ac:dyDescent="0.15">
-      <c r="E131" s="45" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="132" spans="5:5" x14ac:dyDescent="0.15">
-      <c r="E132" s="45" t="s">
-        <v>138</v>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A133" s="53"/>
+      <c r="E133" s="43" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A134" s="53"/>
+      <c r="E134" s="43" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A135" s="53"/>
+      <c r="E135" s="43" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A136" s="53"/>
+      <c r="D136" s="43" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A137" s="53"/>
+      <c r="E137" s="43" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A138" s="53"/>
+      <c r="E138" s="43" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A139" s="53"/>
+      <c r="D139" s="43" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A140" s="53"/>
+      <c r="E140" s="43" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A141" s="53"/>
+      <c r="E141" s="43" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D142" s="43" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="E143" s="43" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="E144" s="43" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A145" s="54"/>
+      <c r="D145" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="O145" s="47"/>
+      <c r="P145" s="47"/>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="E146" s="43" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="E147" s="43" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="E148" s="43" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="E149" s="43" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="E150" s="43" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="E151" s="43" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -10473,13 +10539,12 @@
   <phoneticPr fontId="4"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" firstPageNumber="4" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <headerFooter scaleWithDoc="0" alignWithMargins="0">
-    <oddFooter>&amp;LCopyright(c) 2016 TIS Inc.</oddFooter>
-  </headerFooter>
-  <rowBreaks count="3" manualBreakCount="3">
-    <brk id="34" max="34" man="1"/>
-    <brk id="81" max="34" man="1"/>
-    <brk id="104" max="34" man="1"/>
+  <headerFooter scaleWithDoc="0" alignWithMargins="0"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="39" max="34" man="1"/>
+    <brk id="76" max="34" man="1"/>
+    <brk id="98" max="34" man="1"/>
+    <brk id="121" max="34" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>